--- a/packages/calculators/src/modules/test/6.3-leaching-runoff.xlsx
+++ b/packages/calculators/src/modules/test/6.3-leaching-runoff.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators/packages/calculators/src/modules/test/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators-internal/packages/calculators/src/modules/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0169EE45-E4C2-FA45-9C10-ADB8BC14F8E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7FCE1A5-E625-E34C-BFF2-2AF28941A4D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15940" activeTab="1" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15940" activeTab="1" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
   <sheets>
     <sheet name="6.3.1.1 pasture" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="102">
   <si>
     <t>Method 1</t>
   </si>
@@ -681,9 +681,6 @@
     <t>State</t>
   </si>
   <si>
-    <t>Area sown hectares</t>
-  </si>
-  <si>
     <t>Fc</t>
   </si>
   <si>
@@ -741,7 +738,7 @@
     <t>SA</t>
   </si>
   <si>
-    <t>Hops</t>
+    <t>Hops and grape vines</t>
   </si>
   <si>
     <t>Forage Crops</t>
@@ -1328,10 +1325,10 @@
     </row>
     <row r="2" spans="1:20">
       <c r="E2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -1345,7 +1342,7 @@
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>17</v>
@@ -1366,7 +1363,7 @@
       <c r="A4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="0" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -1426,8 +1423,8 @@
         <v>5000</v>
       </c>
       <c r="E5">
-        <f>IF(ISBLANK(B5), "", VLOOKUP(C5, $R$20:$W$24,2, FALSE)/1000)</f>
-        <v>4.4099999999999999E-3</v>
+        <f>IF(ISBLANK(B5), "", VLOOKUP(C5, $R$20:$W$24,2, FALSE))</f>
+        <v>4.41</v>
       </c>
       <c r="F5" s="12">
         <f t="shared" ref="F5:F10" si="0">IF(ISBLANK(B5), "", VLOOKUP(C5, $R$20:$W$24,6, FALSE))</f>
@@ -1447,8 +1444,8 @@
       </c>
       <c r="J5" s="12"/>
       <c r="K5">
-        <f>IF(ISBLANK(B5),"", (D5*(E5 * 1000) *(1 - F5)*G5)+(D5*(E5*1000)*H5*I5))</f>
-        <v>171.98999999999998</v>
+        <f>IF(ISBLANK(B5),"", (D5*(E5 * 10^-3) *(1 - F5)*G5)+(D5*(E5*10^-3)*H5*I5))</f>
+        <v>0.17198999999999998</v>
       </c>
       <c r="L5">
         <f>IF(ISBLANK(A5), "", IF(A5="yes", 1, 0))</f>
@@ -1460,15 +1457,15 @@
       </c>
       <c r="N5">
         <f>K5*L5*M5</f>
-        <v>41.277599999999993</v>
+        <v>4.1277599999999991E-2</v>
       </c>
       <c r="O5">
         <f>IF(ISBLANK(B5),"",$S$8)</f>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="P5">
-        <f>IF(ISBLANK(B5), "", N5*O5*$S$10/1000)</f>
-        <v>7.1351279999999986E-4</v>
+        <f>IF(ISBLANK(B5), "", N5*O5*$S$10 * 10^3)</f>
+        <v>0.71351279999999973</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -1485,8 +1482,8 @@
         <v>50</v>
       </c>
       <c r="E6">
-        <f t="shared" ref="E6:E10" si="4">IF(ISBLANK(B6), "", VLOOKUP(C6, $R$20:$W$24,2, FALSE)/1000)</f>
-        <v>4.4099999999999999E-3</v>
+        <f t="shared" ref="E6:E10" si="4">IF(ISBLANK(B6), "", VLOOKUP(C6, $R$20:$W$24,2, FALSE))</f>
+        <v>4.41</v>
       </c>
       <c r="F6" s="12">
         <f t="shared" si="0"/>
@@ -1506,8 +1503,8 @@
       </c>
       <c r="J6" s="12"/>
       <c r="K6">
-        <f t="shared" ref="K6:K10" si="5">IF(ISBLANK(B6),"", (D6*(E6 * 1000) *(1 - F6)*G6)+(D6*(E6*1000)*H6*I6))</f>
-        <v>1.7198999999999998</v>
+        <f t="shared" ref="K6:K10" si="5">IF(ISBLANK(B6),"", (D6*(E6 * 10^-3) *(1 - F6)*G6)+(D6*(E6*10^-3)*H6*I6))</f>
+        <v>1.7198999999999999E-3</v>
       </c>
       <c r="L6">
         <f t="shared" ref="L6:L14" si="6">IF(ISBLANK(A6), "", IF(A6="yes", 1, 0))</f>
@@ -1526,7 +1523,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="P6">
-        <f t="shared" ref="P6:P14" si="10">IF(ISBLANK(B6), "", N6*O6*$S$10/1000)</f>
+        <f t="shared" ref="P6:P10" si="10">IF(ISBLANK(B6), "", N6*O6*$S$10 * 10^3)</f>
         <v>0</v>
       </c>
     </row>
@@ -1545,7 +1542,7 @@
       </c>
       <c r="E7">
         <f t="shared" si="4"/>
-        <v>8.3400000000000002E-3</v>
+        <v>8.34</v>
       </c>
       <c r="F7" s="12">
         <f t="shared" si="0"/>
@@ -1566,7 +1563,7 @@
       <c r="J7" s="12"/>
       <c r="K7">
         <f t="shared" si="5"/>
-        <v>89.071200000000005</v>
+        <v>8.9071200000000017E-2</v>
       </c>
       <c r="L7">
         <f t="shared" si="6"/>
@@ -1578,7 +1575,7 @@
       </c>
       <c r="N7">
         <f t="shared" si="8"/>
-        <v>21.377088000000001</v>
+        <v>2.1377088000000002E-2</v>
       </c>
       <c r="O7">
         <f t="shared" si="9"/>
@@ -1586,7 +1583,7 @@
       </c>
       <c r="P7">
         <f t="shared" si="10"/>
-        <v>3.6951823542857138E-4</v>
+        <v>0.36951823542857143</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -1604,7 +1601,7 @@
       </c>
       <c r="E8">
         <f t="shared" si="4"/>
-        <v>8.6199999999999992E-3</v>
+        <v>8.6199999999999992</v>
       </c>
       <c r="F8" s="12">
         <f t="shared" si="0"/>
@@ -1625,7 +1622,7 @@
       <c r="J8" s="12"/>
       <c r="K8">
         <f t="shared" si="5"/>
-        <v>784.41999999999985</v>
+        <v>0.7844199999999999</v>
       </c>
       <c r="L8">
         <f t="shared" si="6"/>
@@ -1669,7 +1666,7 @@
       </c>
       <c r="E9">
         <f t="shared" si="4"/>
-        <v>5.62E-3</v>
+        <v>5.62</v>
       </c>
       <c r="F9" s="12">
         <f t="shared" si="0"/>
@@ -1690,7 +1687,7 @@
       <c r="J9" s="12"/>
       <c r="K9">
         <f t="shared" si="5"/>
-        <v>3.9901999999999997</v>
+        <v>3.9902000000000002E-3</v>
       </c>
       <c r="L9">
         <f t="shared" si="6"/>
@@ -1702,7 +1699,7 @@
       </c>
       <c r="N9">
         <f t="shared" si="8"/>
-        <v>0.95764799999999994</v>
+        <v>9.5764799999999996E-4</v>
       </c>
       <c r="O9">
         <f t="shared" si="9"/>
@@ -1710,7 +1707,7 @@
       </c>
       <c r="P9">
         <f t="shared" si="10"/>
-        <v>1.655362971428571E-5</v>
+        <v>1.6553629714285714E-2</v>
       </c>
       <c r="R9" s="2" t="s">
         <v>38</v>
@@ -1734,7 +1731,7 @@
       </c>
       <c r="E10">
         <f t="shared" si="4"/>
-        <v>8.3499999999999998E-3</v>
+        <v>8.35</v>
       </c>
       <c r="F10" s="12">
         <f t="shared" si="0"/>
@@ -1755,7 +1752,7 @@
       <c r="J10" s="12"/>
       <c r="K10">
         <f t="shared" si="5"/>
-        <v>5.2604999999999995</v>
+        <v>5.2604999999999996E-3</v>
       </c>
       <c r="L10">
         <f t="shared" si="6"/>
@@ -1804,7 +1801,7 @@
       </c>
       <c r="J11" s="12"/>
       <c r="K11" t="str">
-        <f t="shared" ref="K6:K14" si="15">IF(ISBLANK(B11),"", (D11*(E11/1000) *(1 - F11)*G11)+(D11*(E11/1000)*H11*I11))</f>
+        <f t="shared" ref="K11:K14" si="15">IF(ISBLANK(B11),"", (D11*(E11/1000) *(1 - F11)*G11)+(D11*(E11/1000)*H11*I11))</f>
         <v/>
       </c>
       <c r="L11" t="str">
@@ -1816,7 +1813,7 @@
         <v/>
       </c>
       <c r="P11" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="P11:P14" si="16">IF(ISBLANK(B11), "", N11*O11*$S$10/1000)</f>
         <v/>
       </c>
       <c r="R11" s="2"/>
@@ -1858,7 +1855,7 @@
         <v/>
       </c>
       <c r="P12" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R12" s="2" t="s">
@@ -1902,7 +1899,7 @@
         <v/>
       </c>
       <c r="P13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R13" t="s">
@@ -1945,7 +1942,7 @@
         <v/>
       </c>
       <c r="P14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R14" s="2" t="s">
@@ -2394,69 +2391,69 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C481F442-5EF4-1A4A-85C1-C6F2CC54DF49}">
-  <dimension ref="A1:AF58"/>
+  <dimension ref="A1:AD58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="17">
+    <row r="1" spans="1:24" ht="17">
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:24">
       <c r="B2" s="3"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="V2" s="1"/>
-    </row>
-    <row r="3" spans="1:26" ht="68">
+      <c r="T2" s="1"/>
+    </row>
+    <row r="3" spans="1:24" ht="68">
       <c r="B3" s="3"/>
+      <c r="E3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="G3" s="7" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>102</v>
+        <v>42</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="M3" s="7" t="s">
         <v>44</v>
       </c>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
       <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
-      <c r="S3" s="1"/>
       <c r="T3" s="1"/>
-      <c r="V3" s="1"/>
-    </row>
-    <row r="4" spans="1:26" ht="34">
+    </row>
+    <row r="4" spans="1:24" ht="34">
       <c r="A4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -2468,25 +2465,22 @@
       <c r="E4" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>99</v>
+      <c r="F4" t="s">
+        <v>49</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K4" t="s">
-        <v>53</v>
-      </c>
-      <c r="L4" t="s">
         <v>54</v>
       </c>
       <c r="M4" t="s">
@@ -2495,29 +2489,26 @@
       <c r="O4" t="s">
         <v>56</v>
       </c>
+      <c r="P4" t="s">
+        <v>37</v>
+      </c>
       <c r="Q4" t="s">
+        <v>38</v>
+      </c>
+      <c r="R4" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" t="s">
+        <v>31</v>
+      </c>
+      <c r="T4" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="R4" t="s">
-        <v>37</v>
-      </c>
-      <c r="S4" t="s">
-        <v>38</v>
-      </c>
-      <c r="T4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U4" t="s">
-        <v>31</v>
-      </c>
-      <c r="V4" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="X4" s="6" t="s">
+      <c r="V4" s="6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:24">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -2525,82 +2516,75 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" t="s">
         <v>59</v>
       </c>
-      <c r="D5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5">
-        <v>50</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
+      <c r="E5" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="F5" s="12" cm="1">
+        <f t="array" ref="F5">_xlfn.IFS(ISBLANK(B5), "",C5="Sugar Cane", VLOOKUP(D5, $W$48:$X$50, 2, FALSE),_xlfn.IFNA(MATCH(C5, $V$43:$V$47, 0), FALSE), VLOOKUP(C5, $V$43:$X$47, 3, FALSE), TRUE, VLOOKUP(D5, $W$51:$X$53, 2, FALSE))</f>
+        <v>0</v>
       </c>
       <c r="G5" s="12">
+        <v>10000</v>
+      </c>
+      <c r="H5" s="12">
+        <f>IF(ISBLANK($B5), "", VLOOKUP($C5, $V$22:$AD$39, 2, FALSE))</f>
+        <v>0.25</v>
+      </c>
+      <c r="I5" s="12">
+        <f>IF(ISBLANK($B5), "", VLOOKUP($C5, $V$22:$AD$39, 3, FALSE))</f>
+        <v>0.45</v>
+      </c>
+      <c r="J5" s="12">
+        <f>IF(ISBLANK($B5), "", VLOOKUP($C5, $V$22:$AD$39, 4, FALSE))</f>
         <v>0.2</v>
       </c>
-      <c r="H5" s="12" cm="1">
-        <f t="array" ref="H5">_xlfn.IFS(ISBLANK(B5), "",C5="Sugar Cane", VLOOKUP(D5, $Y$48:$Z$50, 2, FALSE),_xlfn.IFNA(MATCH(C5, $X$43:$X$47, 0), FALSE), VLOOKUP(C5, $X$43:$Z$47, 3, FALSE), TRUE, VLOOKUP(D5, $Y$51:$Z$53, 2, FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="12">
-        <f>IF(ISBLANK(B5), "", E5*(F5*1000))</f>
-        <v>100000</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" ref="J5:J14" si="0">IF(ISBLANK($B5), "", VLOOKUP($C5, $X$22:$AF$39, 2, FALSE))</f>
-        <v>0.25</v>
-      </c>
       <c r="K5" s="12">
-        <f t="shared" ref="K5:K14" si="1">IF(ISBLANK($B5), "", VLOOKUP($C5, $X$22:$AF$39, 3, FALSE))</f>
-        <v>0.45</v>
+        <f>IF(ISBLANK($B5), "", VLOOKUP($C5, $V$22:$AD$39, 6, FALSE))</f>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="L5" s="12">
-        <f t="shared" ref="L5:L14" si="2">IF(ISBLANK($B5), "", VLOOKUP($C5, $X$22:$AF$39, 4, FALSE))</f>
-        <v>0.2</v>
+        <f>IF(K5="n/a",0,K5)</f>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="M5" s="12">
-        <f t="shared" ref="M5:M14" si="3">IF(ISBLANK($B5), "", VLOOKUP($C5, $X$22:$AF$39, 6, FALSE))</f>
-        <v>5.0000000000000001E-3</v>
+        <f>IF(ISBLANK($B5), "", VLOOKUP($C5, $V$22:$AD$39, 7, FALSE))</f>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="N5" s="12">
         <f>IF(M5="n/a",0,M5)</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="O5" s="12">
-        <f t="shared" ref="O5:O14" si="4">IF(ISBLANK($B5), "", VLOOKUP($C5, $X$22:$AF$39, 7, FALSE))</f>
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="P5" s="12">
-        <f>IF(O5="n/a",0,O5)</f>
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="Q5">
-        <f t="shared" ref="Q5:Q14" si="5">IF(ISBLANK(B5),"", (I5*J5*(1 - G5 - H5) * L5*N5)+(I5*J5*K5*L5*P5))</f>
-        <v>35.75</v>
-      </c>
-      <c r="R5">
+      <c r="O5">
+        <f>IF(ISBLANK(B5),"", (G5*H5*(1 - E5 - F5) * J5*L5)+(G5*H5*I5*J5*N5))</f>
+        <v>3.5750000000000002</v>
+      </c>
+      <c r="P5">
         <f>IF(ISBLANK(A5), "", IF(A5="yes", 1, 0))</f>
         <v>1</v>
       </c>
+      <c r="Q5">
+        <f>$W$9</f>
+        <v>0.24</v>
+      </c>
+      <c r="R5">
+        <f>O5*P5*Q5</f>
+        <v>0.85799999999999998</v>
+      </c>
       <c r="S5">
-        <f>$Y$9</f>
-        <v>0.24</v>
+        <f>IF(ISBLANK(B5),"",$W$8)</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="T5">
-        <f>Q5*R5*S5</f>
-        <v>8.58</v>
-      </c>
-      <c r="U5">
-        <f>IF(ISBLANK(B5),"",$Y$8)</f>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V5">
-        <f>IF(ISBLANK(B5), "", T5*U5*$Y$10/1000)</f>
-        <v>1.4831142857142857E-4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26">
+        <f>IF(ISBLANK(B5), "", R5*S5*$W$10/1000)</f>
+        <v>1.4831142857142856E-5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -2608,82 +2592,75 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" t="s">
         <v>59</v>
       </c>
-      <c r="D6" t="s">
-        <v>60</v>
-      </c>
       <c r="E6">
-        <v>50</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
         <v>0.2</v>
       </c>
-      <c r="H6" cm="1">
-        <f t="array" ref="H6">_xlfn.IFS(ISBLANK(B6), "",C6="Sugar Cane", VLOOKUP(D6, $Y$48:$Z$50, 2, FALSE),_xlfn.IFNA(MATCH(C6, $X$43:$X$47, 0), FALSE), VLOOKUP(C6, $X$43:$Z$47, 3, FALSE), TRUE, VLOOKUP(D6, $Y$51:$Z$53, 2, FALSE))</f>
+      <c r="F6" cm="1">
+        <f t="array" ref="F6">_xlfn.IFS(ISBLANK(B6), "",C6="Sugar Cane", VLOOKUP(D6, $W$48:$X$50, 2, FALSE),_xlfn.IFNA(MATCH(C6, $V$43:$V$47, 0), FALSE), VLOOKUP(C6, $V$43:$X$47, 3, FALSE), TRUE, VLOOKUP(D6, $W$51:$X$53, 2, FALSE))</f>
         <v>0</v>
       </c>
+      <c r="G6" s="12">
+        <v>11000</v>
+      </c>
+      <c r="H6" s="12">
+        <f>IF(ISBLANK($B6), "", VLOOKUP($C6, $V$22:$AD$39, 2, FALSE))</f>
+        <v>0.25</v>
+      </c>
       <c r="I6" s="12">
-        <f t="shared" ref="I6:I14" si="6">IF(ISBLANK(B6), "", E6*(F6*1000))</f>
-        <v>100000</v>
+        <f>IF(ISBLANK($B6), "", VLOOKUP($C6, $V$22:$AD$39, 3, FALSE))</f>
+        <v>0.45</v>
       </c>
       <c r="J6" s="12">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f>IF(ISBLANK($B6), "", VLOOKUP($C6, $V$22:$AD$39, 4, FALSE))</f>
+        <v>0.2</v>
       </c>
       <c r="K6" s="12">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
+        <f>IF(ISBLANK($B6), "", VLOOKUP($C6, $V$22:$AD$39, 6, FALSE))</f>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="L6" s="12">
-        <f t="shared" si="2"/>
-        <v>0.2</v>
+        <f t="shared" ref="L6:L14" si="0">IF(K6="n/a",0,K6)</f>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="M6" s="12">
-        <f t="shared" si="3"/>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="N6" s="12">
-        <f t="shared" ref="N6:N14" si="7">IF(M6="n/a",0,M6)</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="O6" s="12">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK($B6), "", VLOOKUP($C6, $V$22:$AD$39, 7, FALSE))</f>
         <v>7.0000000000000001E-3</v>
       </c>
+      <c r="N6">
+        <f t="shared" ref="N6:N14" si="1">IF(M6="n/a",0,M6)</f>
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="O6">
+        <f>IF(ISBLANK(B6),"", (G6*H6*(1 - E6 - F6) * J6*L6)+(G6*H6*I6*J6*N6))</f>
+        <v>3.9325000000000001</v>
+      </c>
       <c r="P6">
-        <f t="shared" ref="P6:P14" si="8">IF(O6="n/a",0,O6)</f>
-        <v>7.0000000000000001E-3</v>
+        <f>IF(ISBLANK(A6), "", IF(A6="yes", 1, 0))</f>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <f t="shared" si="5"/>
-        <v>35.75</v>
+        <f t="shared" ref="Q6:Q14" si="2">$W$9</f>
+        <v>0.24</v>
       </c>
       <c r="R6">
-        <f t="shared" ref="R6:R14" si="9">IF(ISBLANK(A6), "", IF(A6="yes", 1, 0))</f>
+        <f t="shared" ref="R6:R14" si="3">O6*P6*Q6</f>
         <v>0</v>
       </c>
       <c r="S6">
-        <f t="shared" ref="S6:S14" si="10">$Y$9</f>
-        <v>0.24</v>
+        <f>IF(ISBLANK(B6),"",$W$8)</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="T6">
-        <f t="shared" ref="T6:T14" si="11">Q6*R6*S6</f>
+        <f>IF(ISBLANK(B6), "", R6*S6*$W$10/1000)</f>
         <v>0</v>
       </c>
-      <c r="U6">
-        <f t="shared" ref="U6:U14" si="12">IF(ISBLANK(B6),"",$Y$8)</f>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V6">
-        <f t="shared" ref="V6:V14" si="13">IF(ISBLANK(B6), "", T6*U6*$Y$10/1000)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26">
+    </row>
+    <row r="7" spans="1:24">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -2691,82 +2668,75 @@
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7">
-        <v>50</v>
-      </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-      <c r="G7">
         <v>0.2</v>
       </c>
-      <c r="H7" cm="1">
-        <f t="array" ref="H7">_xlfn.IFS(ISBLANK(B7), "",C7="Sugar Cane", VLOOKUP(D7, $Y$48:$Z$50, 2, FALSE),_xlfn.IFNA(MATCH(C7, $X$43:$X$47, 0), FALSE), VLOOKUP(C7, $X$43:$Z$47, 3, FALSE), TRUE, VLOOKUP(D7, $Y$51:$Z$53, 2, FALSE))</f>
+      <c r="F7" cm="1">
+        <f t="array" ref="F7">_xlfn.IFS(ISBLANK(B7), "",C7="Sugar Cane", VLOOKUP(D7, $W$48:$X$50, 2, FALSE),_xlfn.IFNA(MATCH(C7, $V$43:$V$47, 0), FALSE), VLOOKUP(C7, $V$43:$X$47, 3, FALSE), TRUE, VLOOKUP(D7, $W$51:$X$53, 2, FALSE))</f>
         <v>0.06</v>
       </c>
+      <c r="G7" s="12">
+        <v>12000</v>
+      </c>
+      <c r="H7" s="12">
+        <f>IF(ISBLANK($B7), "", VLOOKUP($C7, $V$22:$AD$39, 2, FALSE))</f>
+        <v>1.31</v>
+      </c>
       <c r="I7" s="12">
-        <f t="shared" si="6"/>
-        <v>100000</v>
+        <f>IF(ISBLANK($B7), "", VLOOKUP($C7, $V$22:$AD$39, 3, FALSE))</f>
+        <v>0.16</v>
       </c>
       <c r="J7" s="12">
+        <f>IF(ISBLANK($B7), "", VLOOKUP($C7, $V$22:$AD$39, 4, FALSE))</f>
+        <v>0.8</v>
+      </c>
+      <c r="K7" s="12">
+        <f>IF(ISBLANK($B7), "", VLOOKUP($C7, $V$22:$AD$39, 6, FALSE))</f>
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="L7" s="12">
         <f t="shared" si="0"/>
-        <v>1.31</v>
-      </c>
-      <c r="K7" s="12">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="M7" s="12">
+        <f>IF(ISBLANK($B7), "", VLOOKUP($C7, $V$22:$AD$39, 7, FALSE))</f>
+        <v>0.01</v>
+      </c>
+      <c r="N7">
         <f t="shared" si="1"/>
-        <v>0.16</v>
-      </c>
-      <c r="L7" s="12">
+        <v>0.01</v>
+      </c>
+      <c r="O7">
+        <f>IF(ISBLANK(B7),"", (G7*H7*(1 - E7 - F7) * J7*L7)+(G7*H7*I7*J7*N7))</f>
+        <v>85.265280000000004</v>
+      </c>
+      <c r="P7">
+        <f>IF(ISBLANK(A7), "", IF(A7="yes", 1, 0))</f>
+        <v>1</v>
+      </c>
+      <c r="Q7">
         <f t="shared" si="2"/>
-        <v>0.8</v>
-      </c>
-      <c r="M7" s="12">
+        <v>0.24</v>
+      </c>
+      <c r="R7">
         <f t="shared" si="3"/>
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="N7" s="12">
-        <f t="shared" si="7"/>
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="O7" s="12">
-        <f t="shared" si="4"/>
-        <v>0.01</v>
-      </c>
-      <c r="P7">
-        <f t="shared" si="8"/>
-        <v>0.01</v>
-      </c>
-      <c r="Q7">
-        <f t="shared" si="5"/>
-        <v>710.5440000000001</v>
-      </c>
-      <c r="R7">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>20.4636672</v>
       </c>
       <c r="S7">
-        <f t="shared" si="10"/>
-        <v>0.24</v>
+        <f>IF(ISBLANK(B7),"",$W$8)</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="T7">
-        <f t="shared" si="11"/>
-        <v>170.53056000000001</v>
-      </c>
-      <c r="U7">
-        <f t="shared" si="12"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V7">
-        <f t="shared" si="13"/>
-        <v>2.9477425371428573E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26">
+        <f>IF(ISBLANK(B7), "", R7*S7*$W$10/1000)</f>
+        <v>3.5372910445714281E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -2774,88 +2744,81 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="E8">
-        <v>50</v>
-      </c>
-      <c r="F8">
-        <v>2</v>
-      </c>
-      <c r="G8">
         <v>0.2</v>
       </c>
-      <c r="H8" cm="1">
-        <f t="array" ref="H8">_xlfn.IFS(ISBLANK(B8), "",C8="Sugar Cane", VLOOKUP(D8, $Y$48:$Z$50, 2, FALSE),_xlfn.IFNA(MATCH(C8, $X$43:$X$47, 0), FALSE), VLOOKUP(C8, $X$43:$Z$47, 3, FALSE), TRUE, VLOOKUP(D8, $Y$51:$Z$53, 2, FALSE))</f>
+      <c r="F8" cm="1">
+        <f t="array" ref="F8">_xlfn.IFS(ISBLANK(B8), "",C8="Sugar Cane", VLOOKUP(D8, $W$48:$X$50, 2, FALSE),_xlfn.IFNA(MATCH(C8, $V$43:$V$47, 0), FALSE), VLOOKUP(C8, $V$43:$X$47, 3, FALSE), TRUE, VLOOKUP(D8, $W$51:$X$53, 2, FALSE))</f>
         <v>0.06</v>
       </c>
+      <c r="G8" s="12">
+        <v>13000</v>
+      </c>
+      <c r="H8" s="12">
+        <f>IF(ISBLANK($B8), "", VLOOKUP($C8, $V$22:$AD$39, 2, FALSE))</f>
+        <v>1.31</v>
+      </c>
       <c r="I8" s="12">
-        <f t="shared" si="6"/>
-        <v>100000</v>
+        <f>IF(ISBLANK($B8), "", VLOOKUP($C8, $V$22:$AD$39, 3, FALSE))</f>
+        <v>0.16</v>
       </c>
       <c r="J8" s="12">
+        <f>IF(ISBLANK($B8), "", VLOOKUP($C8, $V$22:$AD$39, 4, FALSE))</f>
+        <v>0.8</v>
+      </c>
+      <c r="K8" s="12">
+        <f>IF(ISBLANK($B8), "", VLOOKUP($C8, $V$22:$AD$39, 6, FALSE))</f>
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="L8" s="12">
         <f t="shared" si="0"/>
-        <v>1.31</v>
-      </c>
-      <c r="K8" s="12">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="M8" s="12">
+        <f>IF(ISBLANK($B8), "", VLOOKUP($C8, $V$22:$AD$39, 7, FALSE))</f>
+        <v>0.01</v>
+      </c>
+      <c r="N8">
         <f t="shared" si="1"/>
-        <v>0.16</v>
-      </c>
-      <c r="L8" s="12">
+        <v>0.01</v>
+      </c>
+      <c r="O8">
+        <f>IF(ISBLANK(B8),"", (G8*H8*(1 - E8 - F8) * J8*L8)+(G8*H8*I8*J8*N8))</f>
+        <v>92.37072000000002</v>
+      </c>
+      <c r="P8">
+        <f>IF(ISBLANK(A8), "", IF(A8="yes", 1, 0))</f>
+        <v>0</v>
+      </c>
+      <c r="Q8">
         <f t="shared" si="2"/>
-        <v>0.8</v>
-      </c>
-      <c r="M8" s="12">
+        <v>0.24</v>
+      </c>
+      <c r="R8">
         <f t="shared" si="3"/>
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="N8" s="12">
-        <f t="shared" si="7"/>
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="O8" s="12">
-        <f t="shared" si="4"/>
-        <v>0.01</v>
-      </c>
-      <c r="P8">
-        <f t="shared" si="8"/>
-        <v>0.01</v>
-      </c>
-      <c r="Q8">
-        <f t="shared" si="5"/>
-        <v>710.5440000000001</v>
-      </c>
-      <c r="R8">
-        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S8">
-        <f t="shared" si="10"/>
-        <v>0.24</v>
+        <f>IF(ISBLANK(B8),"",$W$8)</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="T8">
-        <f t="shared" si="11"/>
+        <f>IF(ISBLANK(B8), "", R8*S8*$W$10/1000)</f>
         <v>0</v>
       </c>
-      <c r="U8">
-        <f t="shared" si="12"/>
+      <c r="V8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="W8" s="2">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="V8">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="X8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Y8" s="2">
-        <v>1.0999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26">
+    </row>
+    <row r="9" spans="1:24">
       <c r="A9" t="s">
         <v>35</v>
       </c>
@@ -2863,88 +2826,81 @@
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="E9">
-        <v>50</v>
-      </c>
-      <c r="F9">
-        <v>2</v>
-      </c>
-      <c r="G9">
         <v>0.2</v>
       </c>
-      <c r="H9" cm="1">
-        <f t="array" ref="H9">_xlfn.IFS(ISBLANK(B9), "",C9="Sugar Cane", VLOOKUP(D9, $Y$48:$Z$50, 2, FALSE),_xlfn.IFNA(MATCH(C9, $X$43:$X$47, 0), FALSE), VLOOKUP(C9, $X$43:$Z$47, 3, FALSE), TRUE, VLOOKUP(D9, $Y$51:$Z$53, 2, FALSE))</f>
+      <c r="F9" cm="1">
+        <f t="array" ref="F9">_xlfn.IFS(ISBLANK(B9), "",C9="Sugar Cane", VLOOKUP(D9, $W$48:$X$50, 2, FALSE),_xlfn.IFNA(MATCH(C9, $V$43:$V$47, 0), FALSE), VLOOKUP(C9, $V$43:$X$47, 3, FALSE), TRUE, VLOOKUP(D9, $W$51:$X$53, 2, FALSE))</f>
         <v>1</v>
       </c>
+      <c r="G9" s="12">
+        <v>14000</v>
+      </c>
+      <c r="H9" s="12">
+        <f>IF(ISBLANK($B9), "", VLOOKUP($C9, $V$22:$AD$39, 2, FALSE))</f>
+        <v>0.34</v>
+      </c>
       <c r="I9" s="12">
-        <f t="shared" si="6"/>
-        <v>100000</v>
+        <f>IF(ISBLANK($B9), "", VLOOKUP($C9, $V$22:$AD$39, 3, FALSE))</f>
+        <v>0.43</v>
       </c>
       <c r="J9" s="12">
+        <f>IF(ISBLANK($B9), "", VLOOKUP($C9, $V$22:$AD$39, 4, FALSE))</f>
+        <v>0.25</v>
+      </c>
+      <c r="K9" s="12">
+        <f>IF(ISBLANK($B9), "", VLOOKUP($C9, $V$22:$AD$39, 6, FALSE))</f>
+        <v>0.02</v>
+      </c>
+      <c r="L9" s="12">
         <f t="shared" si="0"/>
-        <v>0.34</v>
-      </c>
-      <c r="K9" s="12">
+        <v>0.02</v>
+      </c>
+      <c r="M9" s="12">
+        <f>IF(ISBLANK($B9), "", VLOOKUP($C9, $V$22:$AD$39, 7, FALSE))</f>
+        <v>0.01</v>
+      </c>
+      <c r="N9">
         <f t="shared" si="1"/>
-        <v>0.43</v>
-      </c>
-      <c r="L9" s="12">
+        <v>0.01</v>
+      </c>
+      <c r="O9">
+        <f>IF(ISBLANK(B9),"", (G9*H9*(1 - E9 - F9) * J9*L9)+(G9*H9*I9*J9*N9))</f>
+        <v>0.35700000000000109</v>
+      </c>
+      <c r="P9">
+        <f>IF(ISBLANK(A9), "", IF(A9="yes", 1, 0))</f>
+        <v>1</v>
+      </c>
+      <c r="Q9">
         <f t="shared" si="2"/>
-        <v>0.25</v>
-      </c>
-      <c r="M9" s="12">
+        <v>0.24</v>
+      </c>
+      <c r="R9">
         <f t="shared" si="3"/>
-        <v>0.02</v>
-      </c>
-      <c r="N9" s="12">
-        <f t="shared" si="7"/>
-        <v>0.02</v>
-      </c>
-      <c r="O9" s="12">
-        <f t="shared" si="4"/>
-        <v>0.01</v>
-      </c>
-      <c r="P9">
-        <f t="shared" si="8"/>
-        <v>0.01</v>
-      </c>
-      <c r="Q9">
-        <f t="shared" si="5"/>
-        <v>2.5500000000000114</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>8.5680000000000256E-2</v>
       </c>
       <c r="S9">
-        <f t="shared" si="10"/>
+        <f>IF(ISBLANK(B9),"",$W$8)</f>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="T9">
+        <f>IF(ISBLANK(B9), "", R9*S9*$W$10/1000)</f>
+        <v>1.4810400000000044E-6</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W9" s="2">
         <v>0.24</v>
       </c>
-      <c r="T9">
-        <f t="shared" si="11"/>
-        <v>0.61200000000000265</v>
-      </c>
-      <c r="U9">
-        <f t="shared" si="12"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V9">
-        <f t="shared" si="13"/>
-        <v>1.0578857142857189E-5</v>
-      </c>
-      <c r="X9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y9" s="2">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26">
+    </row>
+    <row r="10" spans="1:24">
       <c r="A10" t="s">
         <v>36</v>
       </c>
@@ -2952,89 +2908,82 @@
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E10">
-        <v>50</v>
-      </c>
-      <c r="F10">
+        <v>0.3</v>
+      </c>
+      <c r="F10" cm="1">
+        <f t="array" ref="F10">_xlfn.IFS(ISBLANK(B10), "",C10="Sugar Cane", VLOOKUP(D10, $W$48:$X$50, 2, FALSE),_xlfn.IFNA(MATCH(C10, $V$43:$V$47, 0), FALSE), VLOOKUP(C10, $V$43:$X$47, 3, FALSE), TRUE, VLOOKUP(D10, $W$51:$X$53, 2, FALSE))</f>
+        <v>1</v>
+      </c>
+      <c r="G10" s="12">
+        <v>15000</v>
+      </c>
+      <c r="H10" s="12">
+        <f>IF(ISBLANK($B10), "", VLOOKUP($C10, $V$22:$AD$39, 2, FALSE))</f>
+        <v>0.34</v>
+      </c>
+      <c r="I10" s="12">
+        <f>IF(ISBLANK($B10), "", VLOOKUP($C10, $V$22:$AD$39, 3, FALSE))</f>
+        <v>0.43</v>
+      </c>
+      <c r="J10" s="12">
+        <f>IF(ISBLANK($B10), "", VLOOKUP($C10, $V$22:$AD$39, 4, FALSE))</f>
+        <v>0.25</v>
+      </c>
+      <c r="K10" s="12">
+        <f>IF(ISBLANK($B10), "", VLOOKUP($C10, $V$22:$AD$39, 6, FALSE))</f>
+        <v>0.02</v>
+      </c>
+      <c r="L10" s="12">
+        <f t="shared" si="0"/>
+        <v>0.02</v>
+      </c>
+      <c r="M10" s="12">
+        <f>IF(ISBLANK($B10), "", VLOOKUP($C10, $V$22:$AD$39, 7, FALSE))</f>
+        <v>0.01</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="1"/>
+        <v>0.01</v>
+      </c>
+      <c r="O10">
+        <f>IF(ISBLANK(B10),"", (G10*H10*(1 - E10 - F10) * J10*L10)+(G10*H10*I10*J10*N10))</f>
+        <v>-2.1675000000000013</v>
+      </c>
+      <c r="P10">
+        <f>IF(ISBLANK(A10), "", IF(A10="yes", 1, 0))</f>
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.24</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <f>IF(ISBLANK(B10),"",$W$8)</f>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="T10">
+        <f>IF(ISBLANK(B10), "", R10*S10*$W$10/1000)</f>
+        <v>0</v>
+      </c>
+      <c r="V10" t="s">
         <v>2</v>
       </c>
-      <c r="G10">
-        <v>0.3</v>
-      </c>
-      <c r="H10" cm="1">
-        <f t="array" ref="H10">_xlfn.IFS(ISBLANK(B10), "",C10="Sugar Cane", VLOOKUP(D10, $Y$48:$Z$50, 2, FALSE),_xlfn.IFNA(MATCH(C10, $X$43:$X$47, 0), FALSE), VLOOKUP(C10, $X$43:$Z$47, 3, FALSE), TRUE, VLOOKUP(D10, $Y$51:$Z$53, 2, FALSE))</f>
-        <v>1</v>
-      </c>
-      <c r="I10" s="12">
-        <f t="shared" si="6"/>
-        <v>100000</v>
-      </c>
-      <c r="J10" s="12">
-        <f t="shared" si="0"/>
-        <v>0.34</v>
-      </c>
-      <c r="K10" s="12">
-        <f t="shared" si="1"/>
-        <v>0.43</v>
-      </c>
-      <c r="L10" s="12">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
-      </c>
-      <c r="M10" s="12">
-        <f t="shared" si="3"/>
-        <v>0.02</v>
-      </c>
-      <c r="N10" s="12">
-        <f t="shared" si="7"/>
-        <v>0.02</v>
-      </c>
-      <c r="O10" s="12">
-        <f t="shared" si="4"/>
-        <v>0.01</v>
-      </c>
-      <c r="P10">
-        <f t="shared" si="8"/>
-        <v>0.01</v>
-      </c>
-      <c r="Q10">
-        <f t="shared" si="5"/>
-        <v>-14.450000000000003</v>
-      </c>
-      <c r="R10">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <f t="shared" si="10"/>
-        <v>0.24</v>
-      </c>
-      <c r="T10">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <f t="shared" si="12"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V10">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="X10" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y10">
+      <c r="W10">
         <f>44/28</f>
         <v>1.5714285714285714</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:24">
       <c r="A11" t="s">
         <v>35</v>
       </c>
@@ -3042,84 +2991,77 @@
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="E11">
-        <v>50</v>
-      </c>
-      <c r="F11">
-        <v>2</v>
-      </c>
-      <c r="G11">
         <v>0.3</v>
       </c>
-      <c r="H11" cm="1">
-        <f t="array" ref="H11">_xlfn.IFS(ISBLANK(B11), "",C11="Sugar Cane", VLOOKUP(D11, $Y$48:$Z$50, 2, FALSE),_xlfn.IFNA(MATCH(C11, $X$43:$X$47, 0), FALSE), VLOOKUP(C11, $X$43:$Z$47, 3, FALSE), TRUE, VLOOKUP(D11, $Y$51:$Z$53, 2, FALSE))</f>
+      <c r="F11" cm="1">
+        <f t="array" ref="F11">_xlfn.IFS(ISBLANK(B11), "",C11="Sugar Cane", VLOOKUP(D11, $W$48:$X$50, 2, FALSE),_xlfn.IFNA(MATCH(C11, $V$43:$V$47, 0), FALSE), VLOOKUP(C11, $V$43:$X$47, 3, FALSE), TRUE, VLOOKUP(D11, $W$51:$X$53, 2, FALSE))</f>
         <v>0</v>
       </c>
+      <c r="G11" s="12">
+        <v>16000</v>
+      </c>
+      <c r="H11" s="12">
+        <f>IF(ISBLANK($B11), "", VLOOKUP($C11, $V$22:$AD$39, 2, FALSE))</f>
+        <v>1.9</v>
+      </c>
       <c r="I11" s="12">
-        <f t="shared" si="6"/>
-        <v>100000</v>
+        <f>IF(ISBLANK($B11), "", VLOOKUP($C11, $V$22:$AD$39, 3, FALSE))</f>
+        <v>0.3</v>
       </c>
       <c r="J11" s="12">
+        <f>IF(ISBLANK($B11), "", VLOOKUP($C11, $V$22:$AD$39, 4, FALSE))</f>
+        <v>0.9</v>
+      </c>
+      <c r="K11" s="12">
+        <f>IF(ISBLANK($B11), "", VLOOKUP($C11, $V$22:$AD$39, 6, FALSE))</f>
+        <v>0.01</v>
+      </c>
+      <c r="L11" s="12">
         <f t="shared" si="0"/>
-        <v>1.9</v>
-      </c>
-      <c r="K11" s="12">
+        <v>0.01</v>
+      </c>
+      <c r="M11" s="12">
+        <f>IF(ISBLANK($B11), "", VLOOKUP($C11, $V$22:$AD$39, 7, FALSE))</f>
+        <v>0.01</v>
+      </c>
+      <c r="N11">
         <f t="shared" si="1"/>
-        <v>0.3</v>
-      </c>
-      <c r="L11" s="12">
+        <v>0.01</v>
+      </c>
+      <c r="O11">
+        <f>IF(ISBLANK(B11),"", (G11*H11*(1 - E11 - F11) * J11*L11)+(G11*H11*I11*J11*N11))</f>
+        <v>273.60000000000002</v>
+      </c>
+      <c r="P11">
+        <f>IF(ISBLANK(A11), "", IF(A11="yes", 1, 0))</f>
+        <v>1</v>
+      </c>
+      <c r="Q11">
         <f t="shared" si="2"/>
-        <v>0.9</v>
-      </c>
-      <c r="M11" s="12">
+        <v>0.24</v>
+      </c>
+      <c r="R11">
         <f t="shared" si="3"/>
-        <v>0.01</v>
-      </c>
-      <c r="N11" s="12">
-        <f t="shared" si="7"/>
-        <v>0.01</v>
-      </c>
-      <c r="O11" s="12">
-        <f t="shared" si="4"/>
-        <v>0.01</v>
-      </c>
-      <c r="P11">
-        <f t="shared" si="8"/>
-        <v>0.01</v>
-      </c>
-      <c r="Q11">
-        <f t="shared" si="5"/>
-        <v>1710</v>
-      </c>
-      <c r="R11">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>65.664000000000001</v>
       </c>
       <c r="S11">
-        <f t="shared" si="10"/>
-        <v>0.24</v>
+        <f>IF(ISBLANK(B11),"",$W$8)</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="T11">
-        <f t="shared" si="11"/>
-        <v>410.4</v>
-      </c>
-      <c r="U11">
-        <f t="shared" si="12"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V11">
-        <f t="shared" si="13"/>
-        <v>7.0940571428571419E-3</v>
-      </c>
-      <c r="X11" s="2"/>
-      <c r="Y11" s="2"/>
-    </row>
-    <row r="12" spans="1:26">
+        <f>IF(ISBLANK(B11), "", R11*S11*$W$10/1000)</f>
+        <v>1.1350491428571427E-3</v>
+      </c>
+      <c r="V11" s="2"/>
+      <c r="W11" s="2"/>
+    </row>
+    <row r="12" spans="1:24">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -3127,86 +3069,79 @@
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E12">
-        <v>50</v>
-      </c>
-      <c r="F12">
-        <v>2</v>
-      </c>
-      <c r="G12">
         <v>0.3</v>
       </c>
-      <c r="H12" cm="1">
-        <f t="array" ref="H12">_xlfn.IFS(ISBLANK(B12), "",C12="Sugar Cane", VLOOKUP(D12, $Y$48:$Z$50, 2, FALSE),_xlfn.IFNA(MATCH(C12, $X$43:$X$47, 0), FALSE), VLOOKUP(C12, $X$43:$Z$47, 3, FALSE), TRUE, VLOOKUP(D12, $Y$51:$Z$53, 2, FALSE))</f>
+      <c r="F12" cm="1">
+        <f t="array" ref="F12">_xlfn.IFS(ISBLANK(B12), "",C12="Sugar Cane", VLOOKUP(D12, $W$48:$X$50, 2, FALSE),_xlfn.IFNA(MATCH(C12, $V$43:$V$47, 0), FALSE), VLOOKUP(C12, $V$43:$X$47, 3, FALSE), TRUE, VLOOKUP(D12, $W$51:$X$53, 2, FALSE))</f>
         <v>0</v>
       </c>
+      <c r="G12" s="12">
+        <v>17000</v>
+      </c>
+      <c r="H12" s="12">
+        <f>IF(ISBLANK($B12), "", VLOOKUP($C12, $V$22:$AD$39, 2, FALSE))</f>
+        <v>1.5</v>
+      </c>
       <c r="I12" s="12">
-        <f t="shared" si="6"/>
-        <v>100000</v>
+        <f>IF(ISBLANK($B12), "", VLOOKUP($C12, $V$22:$AD$39, 3, FALSE))</f>
+        <v>0.28999999999999998</v>
       </c>
       <c r="J12" s="12">
+        <f>IF(ISBLANK($B12), "", VLOOKUP($C12, $V$22:$AD$39, 4, FALSE))</f>
+        <v>0.88</v>
+      </c>
+      <c r="K12" s="12">
+        <f>IF(ISBLANK($B12), "", VLOOKUP($C12, $V$22:$AD$39, 6, FALSE))</f>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="L12" s="12">
         <f t="shared" si="0"/>
-        <v>1.5</v>
-      </c>
-      <c r="K12" s="12">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="M12" s="12" t="str">
+        <f>IF(ISBLANK($B12), "", VLOOKUP($C12, $V$22:$AD$39, 7, FALSE))</f>
+        <v>n/a</v>
+      </c>
+      <c r="N12">
         <f t="shared" si="1"/>
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="L12" s="12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <f>IF(ISBLANK(B12),"", (G12*H12*(1 - E12 - F12) * J12*L12)+(G12*H12*I12*J12*N12))</f>
+        <v>94.248000000000005</v>
+      </c>
+      <c r="P12">
+        <f>IF(ISBLANK(A12), "", IF(A12="yes", 1, 0))</f>
+        <v>0</v>
+      </c>
+      <c r="Q12">
         <f t="shared" si="2"/>
-        <v>0.88</v>
-      </c>
-      <c r="M12" s="12">
+        <v>0.24</v>
+      </c>
+      <c r="R12">
         <f t="shared" si="3"/>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="N12" s="12">
-        <f t="shared" si="7"/>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="O12" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v>n/a</v>
-      </c>
-      <c r="P12">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q12">
-        <f t="shared" si="5"/>
-        <v>554.4</v>
-      </c>
-      <c r="R12">
-        <f t="shared" si="9"/>
+      <c r="S12">
+        <f>IF(ISBLANK(B12),"",$W$8)</f>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="T12">
+        <f>IF(ISBLANK(B12), "", R12*S12*$W$10/1000)</f>
         <v>0</v>
       </c>
-      <c r="S12">
-        <f t="shared" si="10"/>
-        <v>0.24</v>
-      </c>
-      <c r="T12">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <f t="shared" si="12"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V12">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="X12" s="2" t="s">
+      <c r="V12" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Y12" s="2"/>
-    </row>
-    <row r="13" spans="1:26">
+      <c r="W12" s="2"/>
+    </row>
+    <row r="13" spans="1:24">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -3214,85 +3149,78 @@
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E13">
-        <v>50</v>
-      </c>
-      <c r="F13">
-        <v>2</v>
-      </c>
-      <c r="G13">
         <v>0.3</v>
       </c>
-      <c r="H13" cm="1">
-        <f t="array" ref="H13">_xlfn.IFS(ISBLANK(B13), "",C13="Sugar Cane", VLOOKUP(D13, $Y$48:$Z$50, 2, FALSE),_xlfn.IFNA(MATCH(C13, $X$43:$X$47, 0), FALSE), VLOOKUP(C13, $X$43:$Z$47, 3, FALSE), TRUE, VLOOKUP(D13, $Y$51:$Z$53, 2, FALSE))</f>
+      <c r="F13" cm="1">
+        <f t="array" ref="F13">_xlfn.IFS(ISBLANK(B13), "",C13="Sugar Cane", VLOOKUP(D13, $W$48:$X$50, 2, FALSE),_xlfn.IFNA(MATCH(C13, $V$43:$V$47, 0), FALSE), VLOOKUP(C13, $V$43:$X$47, 3, FALSE), TRUE, VLOOKUP(D13, $W$51:$X$53, 2, FALSE))</f>
         <v>0.8</v>
       </c>
+      <c r="G13" s="12">
+        <v>18000</v>
+      </c>
+      <c r="H13" s="12">
+        <f>IF(ISBLANK($B13), "", VLOOKUP($C13, $V$22:$AD$39, 2, FALSE))</f>
+        <v>1.34</v>
+      </c>
       <c r="I13" s="12">
-        <f t="shared" si="6"/>
-        <v>100000</v>
+        <f>IF(ISBLANK($B13), "", VLOOKUP($C13, $V$22:$AD$39, 3, FALSE))</f>
+        <v>0.37</v>
       </c>
       <c r="J13" s="12">
+        <f>IF(ISBLANK($B13), "", VLOOKUP($C13, $V$22:$AD$39, 4, FALSE))</f>
+        <v>0.88</v>
+      </c>
+      <c r="K13" s="12">
+        <f>IF(ISBLANK($B13), "", VLOOKUP($C13, $V$22:$AD$39, 6, FALSE))</f>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="L13" s="12">
         <f t="shared" si="0"/>
-        <v>1.34</v>
-      </c>
-      <c r="K13" s="12">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="M13" s="12">
+        <f>IF(ISBLANK($B13), "", VLOOKUP($C13, $V$22:$AD$39, 7, FALSE))</f>
+        <v>0.01</v>
+      </c>
+      <c r="N13">
         <f t="shared" si="1"/>
-        <v>0.37</v>
-      </c>
-      <c r="L13" s="12">
+        <v>0.01</v>
+      </c>
+      <c r="O13">
+        <f>IF(ISBLANK(B13),"", (G13*H13*(1 - E13 - F13) * J13*L13)+(G13*H13*I13*J13*N13))</f>
+        <v>65.799359999999979</v>
+      </c>
+      <c r="P13">
+        <f>IF(ISBLANK(A13), "", IF(A13="yes", 1, 0))</f>
+        <v>1</v>
+      </c>
+      <c r="Q13">
         <f t="shared" si="2"/>
-        <v>0.88</v>
-      </c>
-      <c r="M13" s="12">
+        <v>0.24</v>
+      </c>
+      <c r="R13">
         <f t="shared" si="3"/>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="N13" s="12">
-        <f t="shared" si="7"/>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="O13" s="12">
-        <f t="shared" si="4"/>
-        <v>0.01</v>
-      </c>
-      <c r="P13">
-        <f t="shared" si="8"/>
-        <v>0.01</v>
-      </c>
-      <c r="Q13">
-        <f t="shared" si="5"/>
-        <v>365.55199999999996</v>
-      </c>
-      <c r="R13">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>15.791846399999994</v>
       </c>
       <c r="S13">
-        <f t="shared" si="10"/>
-        <v>0.24</v>
+        <f>IF(ISBLANK(B13),"",$W$8)</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="T13">
-        <f t="shared" si="11"/>
-        <v>87.732479999999981</v>
-      </c>
-      <c r="U13">
-        <f t="shared" si="12"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V13">
-        <f t="shared" si="13"/>
-        <v>1.5165185828571424E-3</v>
-      </c>
-      <c r="X13" t="s">
+        <f>IF(ISBLANK(B13), "", R13*S13*$W$10/1000)</f>
+        <v>2.7297334491428559E-4</v>
+      </c>
+      <c r="V13" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:24">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -3300,978 +3228,955 @@
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E14">
-        <v>50</v>
-      </c>
-      <c r="F14">
-        <v>2</v>
-      </c>
-      <c r="G14">
         <v>0.3</v>
       </c>
-      <c r="H14" cm="1">
-        <f t="array" ref="H14">_xlfn.IFS(ISBLANK(B14), "",C14="Sugar Cane", VLOOKUP(D14, $Y$48:$Z$50, 2, FALSE),_xlfn.IFNA(MATCH(C14, $X$43:$X$47, 0), FALSE), VLOOKUP(C14, $X$43:$Z$47, 3, FALSE), TRUE, VLOOKUP(D14, $Y$51:$Z$53, 2, FALSE))</f>
+      <c r="F14" cm="1">
+        <f t="array" ref="F14">_xlfn.IFS(ISBLANK(B14), "",C14="Sugar Cane", VLOOKUP(D14, $W$48:$X$50, 2, FALSE),_xlfn.IFNA(MATCH(C14, $V$43:$V$47, 0), FALSE), VLOOKUP(C14, $V$43:$X$47, 3, FALSE), TRUE, VLOOKUP(D14, $W$51:$X$53, 2, FALSE))</f>
         <v>7.0000000000000007E-2</v>
       </c>
+      <c r="G14" s="12">
+        <v>19000</v>
+      </c>
+      <c r="H14" s="12">
+        <f>IF(ISBLANK($B14), "", VLOOKUP($C14, $V$22:$AD$39, 2, FALSE))</f>
+        <v>1.37</v>
+      </c>
       <c r="I14" s="12">
-        <f t="shared" si="6"/>
-        <v>100000</v>
+        <f>IF(ISBLANK($B14), "", VLOOKUP($C14, $V$22:$AD$39, 3, FALSE))</f>
+        <v>0.51</v>
       </c>
       <c r="J14" s="12">
+        <f>IF(ISBLANK($B14), "", VLOOKUP($C14, $V$22:$AD$39, 4, FALSE))</f>
+        <v>0.87</v>
+      </c>
+      <c r="K14" s="12">
+        <f>IF(ISBLANK($B14), "", VLOOKUP($C14, $V$22:$AD$39, 6, FALSE))</f>
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="L14" s="12">
         <f t="shared" si="0"/>
-        <v>1.37</v>
-      </c>
-      <c r="K14" s="12">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="M14" s="12">
+        <f>IF(ISBLANK($B14), "", VLOOKUP($C14, $V$22:$AD$39, 7, FALSE))</f>
+        <v>0.01</v>
+      </c>
+      <c r="N14">
         <f t="shared" si="1"/>
-        <v>0.51</v>
-      </c>
-      <c r="L14" s="12">
+        <v>0.01</v>
+      </c>
+      <c r="O14">
+        <f>IF(ISBLANK(B14),"", (G14*H14*(1 - E14 - F14) * J14*L14)+(G14*H14*I14*J14*N14))</f>
+        <v>243.89849700000002</v>
+      </c>
+      <c r="P14">
+        <f>IF(ISBLANK(A14), "", IF(A14="yes", 1, 0))</f>
+        <v>0</v>
+      </c>
+      <c r="Q14">
         <f t="shared" si="2"/>
-        <v>0.87</v>
-      </c>
-      <c r="M14" s="12">
+        <v>0.24</v>
+      </c>
+      <c r="R14">
         <f t="shared" si="3"/>
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="N14" s="12">
-        <f t="shared" si="7"/>
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="O14" s="12">
-        <f t="shared" si="4"/>
-        <v>0.01</v>
-      </c>
-      <c r="P14">
-        <f t="shared" si="8"/>
-        <v>0.01</v>
-      </c>
-      <c r="Q14">
-        <f t="shared" si="5"/>
-        <v>1283.6762999999999</v>
-      </c>
-      <c r="R14">
-        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S14">
-        <f t="shared" si="10"/>
-        <v>0.24</v>
+        <f>IF(ISBLANK(B14),"",$W$8)</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="T14">
-        <f t="shared" si="11"/>
+        <f>IF(ISBLANK(B14), "", R14*S14*$W$10/1000)</f>
         <v>0</v>
       </c>
-      <c r="U14">
-        <f t="shared" si="12"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V14">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="X14" s="2" t="s">
+      <c r="V14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="Y14" s="2">
+      <c r="W14" s="2">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="Z14" s="8" t="s">
+      <c r="X14" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:24">
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="14"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
       <c r="J15" s="12"/>
       <c r="K15" s="12"/>
       <c r="L15" s="12"/>
       <c r="M15" s="12"/>
-      <c r="N15" s="12"/>
-      <c r="O15" s="12"/>
-      <c r="X15" s="2" t="s">
+      <c r="V15" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="Y15" s="2">
+      <c r="W15" s="2">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="Z15" s="8" t="s">
+      <c r="X15" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:24">
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="14"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
       <c r="J16" s="12"/>
       <c r="K16" s="12"/>
       <c r="L16" s="12"/>
       <c r="M16" s="12"/>
-      <c r="N16" s="12"/>
-      <c r="O16" s="12"/>
-      <c r="X16" s="2"/>
-      <c r="Y16" s="2"/>
-      <c r="Z16" s="8"/>
-    </row>
-    <row r="17" spans="2:32">
+      <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
+      <c r="X16" s="8"/>
+    </row>
+    <row r="17" spans="2:30">
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="14"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12"/>
       <c r="L17" s="12"/>
       <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
-      <c r="O17" s="12"/>
-    </row>
-    <row r="18" spans="2:32">
+    </row>
+    <row r="18" spans="2:30">
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="14"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12"/>
       <c r="L18" s="12"/>
       <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
-      <c r="O18" s="12"/>
-      <c r="X18" s="2"/>
-      <c r="Y18" s="2"/>
-    </row>
-    <row r="19" spans="2:32">
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+    </row>
+    <row r="19" spans="2:30">
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="14"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12"/>
       <c r="L19" s="12"/>
       <c r="M19" s="12"/>
-      <c r="N19" s="12"/>
-      <c r="O19" s="12"/>
-      <c r="X19" s="2"/>
-      <c r="Y19" s="2"/>
-    </row>
-    <row r="20" spans="2:32">
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+    </row>
+    <row r="20" spans="2:30">
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="14"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12"/>
       <c r="L20" s="12"/>
       <c r="M20" s="12"/>
-      <c r="N20" s="12"/>
-      <c r="O20" s="12"/>
-      <c r="X20" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y20" s="2"/>
-      <c r="AB20" s="7"/>
-    </row>
-    <row r="21" spans="2:32" ht="17">
+      <c r="V20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="W20" s="2"/>
+      <c r="Z20" s="7"/>
+    </row>
+    <row r="21" spans="2:30" ht="17">
       <c r="B21" s="3"/>
-      <c r="X21" s="2"/>
-      <c r="Y21" s="2" t="s">
+      <c r="V21" s="2"/>
+      <c r="W21" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="X21" t="s">
         <v>52</v>
       </c>
-      <c r="Z21" t="s">
+      <c r="Y21" t="s">
         <v>53</v>
+      </c>
+      <c r="Z21" s="7" t="s">
+        <v>91</v>
       </c>
       <c r="AA21" t="s">
         <v>54</v>
       </c>
-      <c r="AB21" s="7" t="s">
+      <c r="AB21" t="s">
         <v>92</v>
       </c>
       <c r="AC21" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="AD21" t="s">
-        <v>93</v>
-      </c>
-      <c r="AE21" t="s">
         <v>94</v>
       </c>
-      <c r="AF21" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="22" spans="2:32">
+    </row>
+    <row r="22" spans="2:30">
       <c r="B22" s="3"/>
-      <c r="X22" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y22" s="11">
+      <c r="V22" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="W22" s="11">
         <v>1.5</v>
       </c>
+      <c r="X22" s="10">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="Y22" s="10">
+        <v>0.88</v>
+      </c>
       <c r="Z22" s="10">
-        <v>0.28999999999999998</v>
+        <v>0.4</v>
       </c>
       <c r="AA22" s="10">
-        <v>0.88</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="AB22" s="10">
-        <v>0.4</v>
+        <v>0.01</v>
       </c>
       <c r="AC22" s="10">
-        <v>6.0000000000000001E-3</v>
+        <v>0.5</v>
       </c>
       <c r="AD22" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AE22" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="AF22" s="10">
         <v>0.9</v>
       </c>
     </row>
-    <row r="23" spans="2:32">
+    <row r="23" spans="2:30">
       <c r="B23" s="3"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
-      <c r="O23" s="12"/>
-      <c r="X23" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y23" s="11">
+      <c r="M23" s="12"/>
+      <c r="V23" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="W23" s="11">
         <v>1.24</v>
       </c>
+      <c r="X23" s="10">
+        <v>0.32</v>
+      </c>
+      <c r="Y23" s="10">
+        <v>0.88</v>
+      </c>
       <c r="Z23" s="10">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="AA23" s="10">
-        <v>0.88</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="AB23" s="10">
-        <v>0.4</v>
+        <v>0.01</v>
       </c>
       <c r="AC23" s="10">
-        <v>7.0000000000000001E-3</v>
+        <v>0.5</v>
       </c>
       <c r="AD23" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AE23" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="AF23" s="10">
         <v>0.85</v>
       </c>
     </row>
-    <row r="24" spans="2:32">
+    <row r="24" spans="2:30">
       <c r="B24" s="3"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
-      <c r="X24" s="2" t="s">
+      <c r="V24" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="W24" s="11">
+        <v>0.81</v>
+      </c>
+      <c r="X24" s="10">
+        <v>0.39</v>
+      </c>
+      <c r="Y24" s="10">
+        <v>0.85</v>
+      </c>
+      <c r="Z24" s="10">
+        <v>0.42</v>
+      </c>
+      <c r="AA24" s="10">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AB24" s="10">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="AC24" s="10">
+        <v>1</v>
+      </c>
+      <c r="AD24" s="10">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="25" spans="2:30">
+      <c r="B25" s="3"/>
+      <c r="V25" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="Y24" s="11">
-        <v>0.81</v>
-      </c>
-      <c r="Z24" s="10">
-        <v>0.39</v>
-      </c>
-      <c r="AA24" s="10">
+      <c r="W25" s="11">
+        <v>1.42</v>
+      </c>
+      <c r="X25" s="10">
+        <v>0.43</v>
+      </c>
+      <c r="Y25" s="10">
+        <v>0.88</v>
+      </c>
+      <c r="Z25" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="AA25" s="10">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="AB25" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="AC25" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AD25" s="10">
         <v>0.85</v>
       </c>
-      <c r="AB24" s="10">
+    </row>
+    <row r="26" spans="2:30">
+      <c r="B26" s="3"/>
+      <c r="V26" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="W26" s="11">
+        <v>1.31</v>
+      </c>
+      <c r="X26" s="10">
+        <v>0.16</v>
+      </c>
+      <c r="Y26" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="Z26" s="10">
         <v>0.42</v>
       </c>
-      <c r="AC24" s="10">
+      <c r="AA26" s="10">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="AB26" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="AC26" s="10">
+        <v>1</v>
+      </c>
+      <c r="AD26" s="10">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="27" spans="2:30">
+      <c r="B27" s="3"/>
+      <c r="V27" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="W27" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="X27" s="10">
+        <v>0.22</v>
+      </c>
+      <c r="Y27" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="Z27" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="AA27" s="10">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="AB27" s="10">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="AC27" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AD27" s="10">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="28" spans="2:30">
+      <c r="B28" s="3"/>
+      <c r="V28" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="W28" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="X28" s="10">
+        <v>0.42</v>
+      </c>
+      <c r="Y28" s="10">
+        <v>0.88</v>
+      </c>
+      <c r="Z28" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="AA28" s="10">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="AB28" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="AC28" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AD28" s="10">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="29" spans="2:30">
+      <c r="B29" s="3"/>
+      <c r="V29" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="W29" s="11">
+        <v>1.46</v>
+      </c>
+      <c r="X29" s="10">
+        <v>0.36</v>
+      </c>
+      <c r="Y29" s="10">
+        <v>0.88</v>
+      </c>
+      <c r="Z29" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="AA29" s="10">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="AB29" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="AC29" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AD29" s="10">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="30" spans="2:30">
+      <c r="B30" s="3"/>
+      <c r="V30" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="W30" s="11">
+        <v>1.37</v>
+      </c>
+      <c r="X30" s="10">
+        <v>0.51</v>
+      </c>
+      <c r="Y30" s="10">
+        <v>0.87</v>
+      </c>
+      <c r="Z30" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="AA30" s="10">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="AB30" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="AC30" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AD30" s="10">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="31" spans="2:30">
+      <c r="B31" s="3"/>
+      <c r="V31" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="W31" s="11">
+        <v>0.34</v>
+      </c>
+      <c r="X31" s="10">
+        <v>0.43</v>
+      </c>
+      <c r="Y31" s="10">
+        <v>0.25</v>
+      </c>
+      <c r="Z31" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="AA31" s="10">
+        <v>0.02</v>
+      </c>
+      <c r="AB31" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="AC31" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD31" s="10">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="32" spans="2:30">
+      <c r="B32" s="3"/>
+      <c r="V32" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="W32" s="11">
+        <v>1.07</v>
+      </c>
+      <c r="X32" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="Y32" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="Z32" s="10">
+        <v>0.42</v>
+      </c>
+      <c r="AA32" s="10">
+        <v>1.6E-2</v>
+      </c>
+      <c r="AB32" s="10">
+        <v>1.4E-2</v>
+      </c>
+      <c r="AC32" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AD32" s="10">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30">
+      <c r="B33" s="3"/>
+      <c r="V33" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="W33" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="X33" s="10">
+        <v>0.45</v>
+      </c>
+      <c r="Y33" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="Z33" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="AA33" s="10">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="AD24" s="10">
+      <c r="AB33" s="10">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="AE24" s="10">
+      <c r="AC33" s="10">
         <v>1</v>
       </c>
-      <c r="AF24" s="10">
+      <c r="AD33" s="10">
         <v>0.8</v>
       </c>
     </row>
-    <row r="25" spans="2:32">
-      <c r="B25" s="3"/>
-      <c r="Q25" t="str">
-        <f>IF(ISBLANK(E25), "", J25/E25)</f>
-        <v/>
-      </c>
-      <c r="X25" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y25" s="11">
-        <v>1.42</v>
-      </c>
-      <c r="Z25" s="10">
-        <v>0.43</v>
-      </c>
-      <c r="AA25" s="10">
+    <row r="34" spans="2:30">
+      <c r="B34" s="3"/>
+      <c r="V34" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="W34" s="11">
+        <v>1.9</v>
+      </c>
+      <c r="X34" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="Y34" s="10">
+        <v>0.9</v>
+      </c>
+      <c r="Z34" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="AA34" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="AB34" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="AC34" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD34" s="10">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30">
+      <c r="B35" s="3"/>
+      <c r="V35" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="W35" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="X35" s="10">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="Y35" s="10">
         <v>0.88</v>
       </c>
-      <c r="AB25" s="10">
+      <c r="Z35" s="10">
         <v>0.4</v>
       </c>
-      <c r="AC25" s="10">
+      <c r="AA35" s="10">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="AD25" s="10">
+      <c r="AB35" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="AC35" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="AD35" s="10">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="36" spans="2:30">
+      <c r="B36" s="3"/>
+      <c r="V36" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="W36" s="11">
+        <v>2.08</v>
+      </c>
+      <c r="X36" s="10">
+        <v>0.33</v>
+      </c>
+      <c r="Y36" s="10">
+        <v>0.96</v>
+      </c>
+      <c r="Z36" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="AA36" s="10">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="AB36" s="10">
         <v>0.01</v>
       </c>
-      <c r="AE25" s="10">
+      <c r="AC36" s="10">
         <v>0.5</v>
       </c>
-      <c r="AF25" s="10">
+      <c r="AD36" s="10">
         <v>0.85</v>
       </c>
     </row>
-    <row r="26" spans="2:32">
-      <c r="B26" s="3"/>
-      <c r="Q26" t="str">
-        <f>IF(ISBLANK(E26), "", J26/E26)</f>
-        <v/>
-      </c>
-      <c r="X26" s="2" t="s">
+    <row r="37" spans="2:30">
+      <c r="B37" s="3"/>
+      <c r="V37" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="W37" s="11">
+        <v>1.34</v>
+      </c>
+      <c r="X37" s="10">
+        <v>0.37</v>
+      </c>
+      <c r="Y37" s="10">
+        <v>0.88</v>
+      </c>
+      <c r="Z37" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="AA37" s="10">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="AB37" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="AC37" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD37" s="10">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="38" spans="2:30">
+      <c r="B38" s="3"/>
+      <c r="V38" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="W38" s="9">
+        <v>1</v>
+      </c>
+      <c r="X38" s="9">
+        <v>0.22</v>
+      </c>
+      <c r="Y38" s="9">
+        <v>0.85</v>
+      </c>
+      <c r="Z38" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="AA38" s="9">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="AB38" s="9">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="AC38" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD38" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30">
+      <c r="B39" s="3"/>
+      <c r="V39" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="W39" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="X39" s="9">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="Y39" s="9">
+        <v>0.88</v>
+      </c>
+      <c r="Z39" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="AA39" s="9">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="AB39" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC39" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD39" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="40" spans="2:30">
+      <c r="B40" s="3"/>
+      <c r="V40" s="2"/>
+      <c r="W40" s="11"/>
+      <c r="X40" s="10"/>
+    </row>
+    <row r="41" spans="2:30">
+      <c r="B41" s="3"/>
+      <c r="V41" s="2"/>
+      <c r="W41" s="2"/>
+    </row>
+    <row r="42" spans="2:30">
+      <c r="B42" s="3"/>
+      <c r="V42" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="W42" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="X42" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30">
+      <c r="B43" s="3"/>
+      <c r="V43" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="W43" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="X43">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30">
+      <c r="B44" s="3"/>
+      <c r="V44" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="W44" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="X44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30">
+      <c r="B45" s="3"/>
+      <c r="V45" t="s">
+        <v>65</v>
+      </c>
+      <c r="W45" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="X45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30">
+      <c r="B46" s="3"/>
+      <c r="V46" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="W46" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="X46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30">
+      <c r="B47" s="3"/>
+      <c r="V47" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="W47" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="X47">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30">
+      <c r="B48" s="3"/>
+      <c r="V48" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="W48" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="X48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:24">
+      <c r="B49" s="3"/>
+      <c r="V49" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="W49" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="X49">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="50" spans="2:24">
+      <c r="B50" s="3"/>
+      <c r="V50" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="W50" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="X50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:24">
+      <c r="B51" s="3"/>
+      <c r="V51" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="W51" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="X51">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="52" spans="2:24">
+      <c r="B52" s="3"/>
+      <c r="V52" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="W52" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="Y26" s="11">
-        <v>1.31</v>
-      </c>
-      <c r="Z26" s="10">
+      <c r="X52">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="2:24">
+      <c r="B53" s="3"/>
+      <c r="V53" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="W53" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="X53">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="54" spans="2:24">
+      <c r="B54" s="3"/>
+      <c r="V54" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="W54" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="X54">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="55" spans="2:24">
+      <c r="B55" s="3"/>
+      <c r="V55" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="W55" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="X55">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="56" spans="2:24">
+      <c r="B56" s="3"/>
+      <c r="V56" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="W56" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="X56">
         <v>0.16</v>
       </c>
-      <c r="AA26" s="10">
-        <v>0.8</v>
-      </c>
-      <c r="AB26" s="10">
-        <v>0.42</v>
-      </c>
-      <c r="AC26" s="10">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="AD26" s="10">
+    </row>
+    <row r="57" spans="2:24">
+      <c r="B57" s="3"/>
+      <c r="V57" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="W57" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="X57">
         <v>0.01</v>
       </c>
-      <c r="AE26" s="10">
-        <v>1</v>
-      </c>
-      <c r="AF26" s="10">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="27" spans="2:32">
-      <c r="B27" s="3"/>
-      <c r="Q27" t="str">
-        <f>IF(ISBLANK(E27), "", J27/E27)</f>
-        <v/>
-      </c>
-      <c r="X27" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y27" s="11">
-        <v>1.5</v>
-      </c>
-      <c r="Z27" s="10">
-        <v>0.22</v>
-      </c>
-      <c r="AA27" s="10">
-        <v>0.8</v>
-      </c>
-      <c r="AB27" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="AC27" s="10">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="AD27" s="10">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="AE27" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="AF27" s="10">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="28" spans="2:32">
-      <c r="B28" s="3"/>
-      <c r="Q28" t="str">
-        <f>IF(ISBLANK(E28), "", J28/E28)</f>
-        <v/>
-      </c>
-      <c r="X28" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y28" s="11">
-        <v>1.5</v>
-      </c>
-      <c r="Z28" s="10">
-        <v>0.42</v>
-      </c>
-      <c r="AA28" s="10">
-        <v>0.88</v>
-      </c>
-      <c r="AB28" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="AC28" s="10">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="AD28" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AE28" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="AF28" s="10">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="29" spans="2:32">
-      <c r="B29" s="3"/>
-      <c r="X29" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="Y29" s="11">
-        <v>1.46</v>
-      </c>
-      <c r="Z29" s="10">
-        <v>0.36</v>
-      </c>
-      <c r="AA29" s="10">
-        <v>0.88</v>
-      </c>
-      <c r="AB29" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="AC29" s="10">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="AD29" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AE29" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="AF29" s="10">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="30" spans="2:32">
-      <c r="B30" s="3"/>
-      <c r="X30" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y30" s="11">
-        <v>1.37</v>
-      </c>
-      <c r="Z30" s="10">
-        <v>0.51</v>
-      </c>
-      <c r="AA30" s="10">
-        <v>0.87</v>
-      </c>
-      <c r="AB30" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="AC30" s="10">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="AD30" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AE30" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="AF30" s="10">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="31" spans="2:32">
-      <c r="B31" s="3"/>
-      <c r="X31" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="Y31" s="11">
-        <v>0.34</v>
-      </c>
-      <c r="Z31" s="10">
-        <v>0.43</v>
-      </c>
-      <c r="AA31" s="10">
-        <v>0.25</v>
-      </c>
-      <c r="AB31" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="AC31" s="10">
-        <v>0.02</v>
-      </c>
-      <c r="AD31" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AE31" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="AF31" s="10">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="32" spans="2:32">
-      <c r="B32" s="3"/>
-      <c r="X32" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y32" s="11">
-        <v>1.07</v>
-      </c>
-      <c r="Z32" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="AA32" s="10">
-        <v>0.8</v>
-      </c>
-      <c r="AB32" s="10">
-        <v>0.42</v>
-      </c>
-      <c r="AC32" s="10">
-        <v>1.6E-2</v>
-      </c>
-      <c r="AD32" s="10">
-        <v>1.4E-2</v>
-      </c>
-      <c r="AE32" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="AF32" s="10">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="33" spans="2:32">
-      <c r="B33" s="3"/>
-      <c r="X33" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="Y33" s="11">
-        <v>0.25</v>
-      </c>
-      <c r="Z33" s="10">
-        <v>0.45</v>
-      </c>
-      <c r="AA33" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="AB33" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="AC33" s="10">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="AD33" s="10">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="AE33" s="10">
-        <v>1</v>
-      </c>
-      <c r="AF33" s="10">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="34" spans="2:32">
-      <c r="B34" s="3"/>
-      <c r="X34" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y34" s="11">
-        <v>1.9</v>
-      </c>
-      <c r="Z34" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="AA34" s="10">
-        <v>0.9</v>
-      </c>
-      <c r="AB34" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="AC34" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AD34" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AE34" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="AF34" s="10">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="35" spans="2:32">
-      <c r="B35" s="3"/>
-      <c r="X35" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y35" s="11">
-        <v>1.5</v>
-      </c>
-      <c r="Z35" s="10">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="AA35" s="10">
-        <v>0.88</v>
-      </c>
-      <c r="AB35" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="AC35" s="10">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="AD35" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="AE35" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AF35" s="10">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="36" spans="2:32">
-      <c r="B36" s="3"/>
-      <c r="X36" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y36" s="11">
-        <v>2.08</v>
-      </c>
-      <c r="Z36" s="10">
-        <v>0.33</v>
-      </c>
-      <c r="AA36" s="10">
-        <v>0.96</v>
-      </c>
-      <c r="AB36" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="AC36" s="10">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="AD36" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AE36" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="AF36" s="10">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="37" spans="2:32">
-      <c r="B37" s="3"/>
-      <c r="X37" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="Y37" s="11">
-        <v>1.34</v>
-      </c>
-      <c r="Z37" s="10">
-        <v>0.37</v>
-      </c>
-      <c r="AA37" s="10">
-        <v>0.88</v>
-      </c>
-      <c r="AB37" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="AC37" s="10">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="AD37" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="AE37" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="AF37" s="10">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="38" spans="2:32">
-      <c r="B38" s="3"/>
-      <c r="X38" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y38" s="9">
-        <v>1</v>
-      </c>
-      <c r="Z38" s="9">
-        <v>0.22</v>
-      </c>
-      <c r="AA38" s="9">
-        <v>0.85</v>
-      </c>
-      <c r="AB38" s="9">
-        <v>0.4</v>
-      </c>
-      <c r="AC38" s="9">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="AD38" s="9">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="AE38" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="AF38" s="9" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="39" spans="2:32">
-      <c r="B39" s="3"/>
-      <c r="X39" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y39" s="9">
-        <v>1.5</v>
-      </c>
-      <c r="Z39" s="9">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="AA39" s="9">
-        <v>0.88</v>
-      </c>
-      <c r="AB39" s="9">
-        <v>0.4</v>
-      </c>
-      <c r="AC39" s="9">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="AD39" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="AE39" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="AF39" s="9" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="40" spans="2:32">
-      <c r="B40" s="3"/>
-      <c r="X40" s="2"/>
-      <c r="Y40" s="11"/>
-      <c r="Z40" s="10"/>
-    </row>
-    <row r="41" spans="2:32">
-      <c r="B41" s="3"/>
-      <c r="X41" s="2"/>
-      <c r="Y41" s="2"/>
-    </row>
-    <row r="42" spans="2:32">
-      <c r="B42" s="3"/>
-      <c r="X42" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y42" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z42" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="43" spans="2:32">
-      <c r="B43" s="3"/>
-      <c r="X43" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y43" s="2" t="s">
+    </row>
+    <row r="58" spans="2:24">
+      <c r="B58" s="3"/>
+      <c r="V58" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="Z43">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="44" spans="2:32">
-      <c r="B44" s="3"/>
-      <c r="X44" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="Y44" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="Z44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="2:32">
-      <c r="B45" s="3"/>
-      <c r="X45" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y45" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="Z45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:32">
-      <c r="B46" s="3"/>
-      <c r="X46" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y46" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="Z46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:32">
-      <c r="B47" s="3"/>
-      <c r="X47" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="Y47" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="Z47">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="48" spans="2:32">
-      <c r="B48" s="3"/>
-      <c r="X48" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y48" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="Z48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="2:26">
-      <c r="B49" s="3"/>
-      <c r="X49" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y49" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z49">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="50" spans="2:26">
-      <c r="B50" s="3"/>
-      <c r="X50" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y50" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="2:26">
-      <c r="B51" s="3"/>
-      <c r="X51" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y51" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="Z51">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="52" spans="2:26">
-      <c r="B52" s="3"/>
-      <c r="X52" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y52" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z52">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="53" spans="2:26">
-      <c r="B53" s="3"/>
-      <c r="X53" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y53" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z53">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="54" spans="2:26">
-      <c r="B54" s="3"/>
-      <c r="X54" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y54" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z54">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="55" spans="2:26">
-      <c r="B55" s="3"/>
-      <c r="X55" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y55" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z55">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="56" spans="2:26">
-      <c r="B56" s="3"/>
-      <c r="X56" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y56" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="Z56">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="57" spans="2:26">
-      <c r="B57" s="3"/>
-      <c r="X57" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y57" s="2" t="s">
+      <c r="W58" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="Z57">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="58" spans="2:26">
-      <c r="B58" s="3"/>
-      <c r="X58" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y58" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="Z58">
+      <c r="X58">
         <v>0</v>
       </c>
     </row>

--- a/packages/calculators/src/modules/test/6.3-leaching-runoff.xlsx
+++ b/packages/calculators/src/modules/test/6.3-leaching-runoff.xlsx
@@ -1,14 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators-internal/packages/calculators/src/modules/test/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7FCE1A5-E625-E34C-BFF2-2AF28941A4D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA133A8-DFDB-4445-8D75-CB895F983103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15940" activeTab="1" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
@@ -16,6 +11,9 @@
     <sheet name="6.3.1.1 pasture" sheetId="1" r:id="rId1"/>
     <sheet name="6.3.1.1 crop" sheetId="3" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -940,7 +938,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -958,9 +956,6 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -978,6 +973,28 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="common"/>
+    </sheetNames>
+    <definedNames>
+      <definedName name="common_cn2o" refersTo="='common'!$B$4"/>
+    </definedNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="4">
+          <cell r="B4">
+            <v>1.57</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1327,7 +1344,7 @@
       <c r="E2" t="s">
         <v>100</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="K2" s="14" t="s">
         <v>99</v>
       </c>
       <c r="L2" s="1"/>
@@ -1363,7 +1380,7 @@
       <c r="A4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -1465,7 +1482,7 @@
       </c>
       <c r="P5">
         <f>IF(ISBLANK(B5), "", N5*O5*$S$10 * 10^3)</f>
-        <v>0.71351279999999973</v>
+        <v>0.71286415199999986</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -1583,7 +1600,7 @@
       </c>
       <c r="P7">
         <f t="shared" si="10"/>
-        <v>0.36951823542857143</v>
+        <v>0.36918230976000005</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -1707,7 +1724,7 @@
       </c>
       <c r="P9">
         <f t="shared" si="10"/>
-        <v>1.6553629714285714E-2</v>
+        <v>1.653858096E-2</v>
       </c>
       <c r="R9" s="2" t="s">
         <v>38</v>
@@ -1778,8 +1795,8 @@
         <v>2</v>
       </c>
       <c r="S10">
-        <f>44/28</f>
-        <v>1.5714285714285714</v>
+        <f>[1]!common_cn2o</f>
+        <v>1.57</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -2532,19 +2549,19 @@
         <v>10000</v>
       </c>
       <c r="H5" s="12">
-        <f>IF(ISBLANK($B5), "", VLOOKUP($C5, $V$22:$AD$39, 2, FALSE))</f>
+        <f t="shared" ref="H5:H14" si="0">IF(ISBLANK($B5), "", VLOOKUP($C5, $V$22:$AD$39, 2, FALSE))</f>
         <v>0.25</v>
       </c>
       <c r="I5" s="12">
-        <f>IF(ISBLANK($B5), "", VLOOKUP($C5, $V$22:$AD$39, 3, FALSE))</f>
+        <f t="shared" ref="I5:I14" si="1">IF(ISBLANK($B5), "", VLOOKUP($C5, $V$22:$AD$39, 3, FALSE))</f>
         <v>0.45</v>
       </c>
       <c r="J5" s="12">
-        <f>IF(ISBLANK($B5), "", VLOOKUP($C5, $V$22:$AD$39, 4, FALSE))</f>
+        <f t="shared" ref="J5:J14" si="2">IF(ISBLANK($B5), "", VLOOKUP($C5, $V$22:$AD$39, 4, FALSE))</f>
         <v>0.2</v>
       </c>
       <c r="K5" s="12">
-        <f>IF(ISBLANK($B5), "", VLOOKUP($C5, $V$22:$AD$39, 6, FALSE))</f>
+        <f t="shared" ref="K5:K14" si="3">IF(ISBLANK($B5), "", VLOOKUP($C5, $V$22:$AD$39, 6, FALSE))</f>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="L5" s="12">
@@ -2552,7 +2569,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="M5" s="12">
-        <f>IF(ISBLANK($B5), "", VLOOKUP($C5, $V$22:$AD$39, 7, FALSE))</f>
+        <f t="shared" ref="M5:M14" si="4">IF(ISBLANK($B5), "", VLOOKUP($C5, $V$22:$AD$39, 7, FALSE))</f>
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="N5" s="12">
@@ -2560,11 +2577,11 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="O5">
-        <f>IF(ISBLANK(B5),"", (G5*H5*(1 - E5 - F5) * J5*L5)+(G5*H5*I5*J5*N5))</f>
+        <f t="shared" ref="O5:O14" si="5">IF(ISBLANK(B5),"", (G5*H5*(1 - E5 - F5) * J5*L5)+(G5*H5*I5*J5*N5))</f>
         <v>3.5750000000000002</v>
       </c>
       <c r="P5">
-        <f>IF(ISBLANK(A5), "", IF(A5="yes", 1, 0))</f>
+        <f t="shared" ref="P5:P14" si="6">IF(ISBLANK(A5), "", IF(A5="yes", 1, 0))</f>
         <v>1</v>
       </c>
       <c r="Q5">
@@ -2576,12 +2593,12 @@
         <v>0.85799999999999998</v>
       </c>
       <c r="S5">
-        <f>IF(ISBLANK(B5),"",$W$8)</f>
+        <f t="shared" ref="S5:S14" si="7">IF(ISBLANK(B5),"",$W$8)</f>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="T5">
-        <f>IF(ISBLANK(B5), "", R5*S5*$W$10/1000)</f>
-        <v>1.4831142857142856E-5</v>
+        <f t="shared" ref="T5:T14" si="8">IF(ISBLANK(B5), "", R5*S5*$W$10/1000)</f>
+        <v>1.4817659999999998E-5</v>
       </c>
     </row>
     <row r="6" spans="1:24">
@@ -2608,55 +2625,55 @@
         <v>11000</v>
       </c>
       <c r="H6" s="12">
-        <f>IF(ISBLANK($B6), "", VLOOKUP($C6, $V$22:$AD$39, 2, FALSE))</f>
+        <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
       <c r="I6" s="12">
-        <f>IF(ISBLANK($B6), "", VLOOKUP($C6, $V$22:$AD$39, 3, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>0.45</v>
       </c>
       <c r="J6" s="12">
-        <f>IF(ISBLANK($B6), "", VLOOKUP($C6, $V$22:$AD$39, 4, FALSE))</f>
+        <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
       <c r="K6" s="12">
-        <f>IF(ISBLANK($B6), "", VLOOKUP($C6, $V$22:$AD$39, 6, FALSE))</f>
+        <f t="shared" si="3"/>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="L6" s="12">
-        <f t="shared" ref="L6:L14" si="0">IF(K6="n/a",0,K6)</f>
+        <f t="shared" ref="L6:L14" si="9">IF(K6="n/a",0,K6)</f>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="M6" s="12">
-        <f>IF(ISBLANK($B6), "", VLOOKUP($C6, $V$22:$AD$39, 7, FALSE))</f>
+        <f t="shared" si="4"/>
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="N6">
-        <f t="shared" ref="N6:N14" si="1">IF(M6="n/a",0,M6)</f>
+        <f t="shared" ref="N6:N14" si="10">IF(M6="n/a",0,M6)</f>
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="O6">
-        <f>IF(ISBLANK(B6),"", (G6*H6*(1 - E6 - F6) * J6*L6)+(G6*H6*I6*J6*N6))</f>
+        <f t="shared" si="5"/>
         <v>3.9325000000000001</v>
       </c>
       <c r="P6">
-        <f>IF(ISBLANK(A6), "", IF(A6="yes", 1, 0))</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q6">
-        <f t="shared" ref="Q6:Q14" si="2">$W$9</f>
+        <f t="shared" ref="Q6:Q14" si="11">$W$9</f>
         <v>0.24</v>
       </c>
       <c r="R6">
-        <f t="shared" ref="R6:R14" si="3">O6*P6*Q6</f>
+        <f t="shared" ref="R6:R14" si="12">O6*P6*Q6</f>
         <v>0</v>
       </c>
       <c r="S6">
-        <f>IF(ISBLANK(B6),"",$W$8)</f>
+        <f t="shared" si="7"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="T6">
-        <f>IF(ISBLANK(B6), "", R6*S6*$W$10/1000)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -2684,56 +2701,56 @@
         <v>12000</v>
       </c>
       <c r="H7" s="12">
-        <f>IF(ISBLANK($B7), "", VLOOKUP($C7, $V$22:$AD$39, 2, FALSE))</f>
+        <f t="shared" si="0"/>
         <v>1.31</v>
       </c>
       <c r="I7" s="12">
-        <f>IF(ISBLANK($B7), "", VLOOKUP($C7, $V$22:$AD$39, 3, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>0.16</v>
       </c>
       <c r="J7" s="12">
-        <f>IF(ISBLANK($B7), "", VLOOKUP($C7, $V$22:$AD$39, 4, FALSE))</f>
+        <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
       <c r="K7" s="12">
-        <f>IF(ISBLANK($B7), "", VLOOKUP($C7, $V$22:$AD$39, 6, FALSE))</f>
+        <f t="shared" si="3"/>
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="L7" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="M7" s="12">
-        <f>IF(ISBLANK($B7), "", VLOOKUP($C7, $V$22:$AD$39, 7, FALSE))</f>
+        <f t="shared" si="4"/>
         <v>0.01</v>
       </c>
       <c r="N7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>0.01</v>
       </c>
       <c r="O7">
-        <f>IF(ISBLANK(B7),"", (G7*H7*(1 - E7 - F7) * J7*L7)+(G7*H7*I7*J7*N7))</f>
+        <f t="shared" si="5"/>
         <v>85.265280000000004</v>
       </c>
       <c r="P7">
-        <f>IF(ISBLANK(A7), "", IF(A7="yes", 1, 0))</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Q7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>0.24</v>
       </c>
       <c r="R7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>20.4636672</v>
       </c>
       <c r="S7">
-        <f>IF(ISBLANK(B7),"",$W$8)</f>
+        <f t="shared" si="7"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="T7">
-        <f>IF(ISBLANK(B7), "", R7*S7*$W$10/1000)</f>
-        <v>3.5372910445714281E-4</v>
+        <f t="shared" si="8"/>
+        <v>3.5340753254399997E-4</v>
       </c>
     </row>
     <row r="8" spans="1:24">
@@ -2760,55 +2777,55 @@
         <v>13000</v>
       </c>
       <c r="H8" s="12">
-        <f>IF(ISBLANK($B8), "", VLOOKUP($C8, $V$22:$AD$39, 2, FALSE))</f>
+        <f t="shared" si="0"/>
         <v>1.31</v>
       </c>
       <c r="I8" s="12">
-        <f>IF(ISBLANK($B8), "", VLOOKUP($C8, $V$22:$AD$39, 3, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>0.16</v>
       </c>
       <c r="J8" s="12">
-        <f>IF(ISBLANK($B8), "", VLOOKUP($C8, $V$22:$AD$39, 4, FALSE))</f>
+        <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
       <c r="K8" s="12">
-        <f>IF(ISBLANK($B8), "", VLOOKUP($C8, $V$22:$AD$39, 6, FALSE))</f>
+        <f t="shared" si="3"/>
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="L8" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="M8" s="12">
-        <f>IF(ISBLANK($B8), "", VLOOKUP($C8, $V$22:$AD$39, 7, FALSE))</f>
+        <f t="shared" si="4"/>
         <v>0.01</v>
       </c>
       <c r="N8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>0.01</v>
       </c>
       <c r="O8">
-        <f>IF(ISBLANK(B8),"", (G8*H8*(1 - E8 - F8) * J8*L8)+(G8*H8*I8*J8*N8))</f>
+        <f t="shared" si="5"/>
         <v>92.37072000000002</v>
       </c>
       <c r="P8">
-        <f>IF(ISBLANK(A8), "", IF(A8="yes", 1, 0))</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>0.24</v>
       </c>
       <c r="R8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S8">
-        <f>IF(ISBLANK(B8),"",$W$8)</f>
+        <f t="shared" si="7"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="T8">
-        <f>IF(ISBLANK(B8), "", R8*S8*$W$10/1000)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V8" s="2" t="s">
@@ -2842,56 +2859,56 @@
         <v>14000</v>
       </c>
       <c r="H9" s="12">
-        <f>IF(ISBLANK($B9), "", VLOOKUP($C9, $V$22:$AD$39, 2, FALSE))</f>
+        <f t="shared" si="0"/>
         <v>0.34</v>
       </c>
       <c r="I9" s="12">
-        <f>IF(ISBLANK($B9), "", VLOOKUP($C9, $V$22:$AD$39, 3, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>0.43</v>
       </c>
       <c r="J9" s="12">
-        <f>IF(ISBLANK($B9), "", VLOOKUP($C9, $V$22:$AD$39, 4, FALSE))</f>
+        <f t="shared" si="2"/>
         <v>0.25</v>
       </c>
       <c r="K9" s="12">
-        <f>IF(ISBLANK($B9), "", VLOOKUP($C9, $V$22:$AD$39, 6, FALSE))</f>
+        <f t="shared" si="3"/>
         <v>0.02</v>
       </c>
       <c r="L9" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>0.02</v>
       </c>
       <c r="M9" s="12">
-        <f>IF(ISBLANK($B9), "", VLOOKUP($C9, $V$22:$AD$39, 7, FALSE))</f>
+        <f t="shared" si="4"/>
         <v>0.01</v>
       </c>
       <c r="N9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>0.01</v>
       </c>
       <c r="O9">
-        <f>IF(ISBLANK(B9),"", (G9*H9*(1 - E9 - F9) * J9*L9)+(G9*H9*I9*J9*N9))</f>
+        <f t="shared" si="5"/>
         <v>0.35700000000000109</v>
       </c>
       <c r="P9">
-        <f>IF(ISBLANK(A9), "", IF(A9="yes", 1, 0))</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Q9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>0.24</v>
       </c>
       <c r="R9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>8.5680000000000256E-2</v>
       </c>
       <c r="S9">
-        <f>IF(ISBLANK(B9),"",$W$8)</f>
+        <f t="shared" si="7"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="T9">
-        <f>IF(ISBLANK(B9), "", R9*S9*$W$10/1000)</f>
-        <v>1.4810400000000044E-6</v>
+        <f t="shared" si="8"/>
+        <v>1.4796936000000045E-6</v>
       </c>
       <c r="V9" s="2" t="s">
         <v>38</v>
@@ -2924,63 +2941,63 @@
         <v>15000</v>
       </c>
       <c r="H10" s="12">
-        <f>IF(ISBLANK($B10), "", VLOOKUP($C10, $V$22:$AD$39, 2, FALSE))</f>
+        <f t="shared" si="0"/>
         <v>0.34</v>
       </c>
       <c r="I10" s="12">
-        <f>IF(ISBLANK($B10), "", VLOOKUP($C10, $V$22:$AD$39, 3, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>0.43</v>
       </c>
       <c r="J10" s="12">
-        <f>IF(ISBLANK($B10), "", VLOOKUP($C10, $V$22:$AD$39, 4, FALSE))</f>
+        <f t="shared" si="2"/>
         <v>0.25</v>
       </c>
       <c r="K10" s="12">
-        <f>IF(ISBLANK($B10), "", VLOOKUP($C10, $V$22:$AD$39, 6, FALSE))</f>
+        <f t="shared" si="3"/>
         <v>0.02</v>
       </c>
       <c r="L10" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>0.02</v>
       </c>
       <c r="M10" s="12">
-        <f>IF(ISBLANK($B10), "", VLOOKUP($C10, $V$22:$AD$39, 7, FALSE))</f>
+        <f t="shared" si="4"/>
         <v>0.01</v>
       </c>
       <c r="N10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>0.01</v>
       </c>
       <c r="O10">
-        <f>IF(ISBLANK(B10),"", (G10*H10*(1 - E10 - F10) * J10*L10)+(G10*H10*I10*J10*N10))</f>
+        <f t="shared" si="5"/>
         <v>-2.1675000000000013</v>
       </c>
       <c r="P10">
-        <f>IF(ISBLANK(A10), "", IF(A10="yes", 1, 0))</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>0.24</v>
       </c>
       <c r="R10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S10">
-        <f>IF(ISBLANK(B10),"",$W$8)</f>
+        <f t="shared" si="7"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="T10">
-        <f>IF(ISBLANK(B10), "", R10*S10*$W$10/1000)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V10" t="s">
         <v>2</v>
       </c>
       <c r="W10">
-        <f>44/28</f>
-        <v>1.5714285714285714</v>
+        <f>[1]!common_cn2o</f>
+        <v>1.57</v>
       </c>
     </row>
     <row r="11" spans="1:24">
@@ -3007,56 +3024,56 @@
         <v>16000</v>
       </c>
       <c r="H11" s="12">
-        <f>IF(ISBLANK($B11), "", VLOOKUP($C11, $V$22:$AD$39, 2, FALSE))</f>
+        <f t="shared" si="0"/>
         <v>1.9</v>
       </c>
       <c r="I11" s="12">
-        <f>IF(ISBLANK($B11), "", VLOOKUP($C11, $V$22:$AD$39, 3, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>0.3</v>
       </c>
       <c r="J11" s="12">
-        <f>IF(ISBLANK($B11), "", VLOOKUP($C11, $V$22:$AD$39, 4, FALSE))</f>
+        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
       <c r="K11" s="12">
-        <f>IF(ISBLANK($B11), "", VLOOKUP($C11, $V$22:$AD$39, 6, FALSE))</f>
+        <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
       <c r="L11" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>0.01</v>
       </c>
       <c r="M11" s="12">
-        <f>IF(ISBLANK($B11), "", VLOOKUP($C11, $V$22:$AD$39, 7, FALSE))</f>
+        <f t="shared" si="4"/>
         <v>0.01</v>
       </c>
       <c r="N11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>0.01</v>
       </c>
       <c r="O11">
-        <f>IF(ISBLANK(B11),"", (G11*H11*(1 - E11 - F11) * J11*L11)+(G11*H11*I11*J11*N11))</f>
+        <f t="shared" si="5"/>
         <v>273.60000000000002</v>
       </c>
       <c r="P11">
-        <f>IF(ISBLANK(A11), "", IF(A11="yes", 1, 0))</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>0.24</v>
       </c>
       <c r="R11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>65.664000000000001</v>
       </c>
       <c r="S11">
-        <f>IF(ISBLANK(B11),"",$W$8)</f>
+        <f t="shared" si="7"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="T11">
-        <f>IF(ISBLANK(B11), "", R11*S11*$W$10/1000)</f>
-        <v>1.1350491428571427E-3</v>
+        <f t="shared" si="8"/>
+        <v>1.1340172799999999E-3</v>
       </c>
       <c r="V11" s="2"/>
       <c r="W11" s="2"/>
@@ -3085,55 +3102,55 @@
         <v>17000</v>
       </c>
       <c r="H12" s="12">
-        <f>IF(ISBLANK($B12), "", VLOOKUP($C12, $V$22:$AD$39, 2, FALSE))</f>
+        <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
       <c r="I12" s="12">
-        <f>IF(ISBLANK($B12), "", VLOOKUP($C12, $V$22:$AD$39, 3, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="J12" s="12">
-        <f>IF(ISBLANK($B12), "", VLOOKUP($C12, $V$22:$AD$39, 4, FALSE))</f>
+        <f t="shared" si="2"/>
         <v>0.88</v>
       </c>
       <c r="K12" s="12">
-        <f>IF(ISBLANK($B12), "", VLOOKUP($C12, $V$22:$AD$39, 6, FALSE))</f>
+        <f t="shared" si="3"/>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="L12" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="M12" s="12" t="str">
-        <f>IF(ISBLANK($B12), "", VLOOKUP($C12, $V$22:$AD$39, 7, FALSE))</f>
+        <f t="shared" si="4"/>
         <v>n/a</v>
       </c>
       <c r="N12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O12">
-        <f>IF(ISBLANK(B12),"", (G12*H12*(1 - E12 - F12) * J12*L12)+(G12*H12*I12*J12*N12))</f>
+        <f t="shared" si="5"/>
         <v>94.248000000000005</v>
       </c>
       <c r="P12">
-        <f>IF(ISBLANK(A12), "", IF(A12="yes", 1, 0))</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>0.24</v>
       </c>
       <c r="R12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S12">
-        <f>IF(ISBLANK(B12),"",$W$8)</f>
+        <f t="shared" si="7"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="T12">
-        <f>IF(ISBLANK(B12), "", R12*S12*$W$10/1000)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V12" s="2" t="s">
@@ -3165,56 +3182,56 @@
         <v>18000</v>
       </c>
       <c r="H13" s="12">
-        <f>IF(ISBLANK($B13), "", VLOOKUP($C13, $V$22:$AD$39, 2, FALSE))</f>
+        <f t="shared" si="0"/>
         <v>1.34</v>
       </c>
       <c r="I13" s="12">
-        <f>IF(ISBLANK($B13), "", VLOOKUP($C13, $V$22:$AD$39, 3, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
       <c r="J13" s="12">
-        <f>IF(ISBLANK($B13), "", VLOOKUP($C13, $V$22:$AD$39, 4, FALSE))</f>
+        <f t="shared" si="2"/>
         <v>0.88</v>
       </c>
       <c r="K13" s="12">
-        <f>IF(ISBLANK($B13), "", VLOOKUP($C13, $V$22:$AD$39, 6, FALSE))</f>
+        <f t="shared" si="3"/>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="L13" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="M13" s="12">
-        <f>IF(ISBLANK($B13), "", VLOOKUP($C13, $V$22:$AD$39, 7, FALSE))</f>
+        <f t="shared" si="4"/>
         <v>0.01</v>
       </c>
       <c r="N13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>0.01</v>
       </c>
       <c r="O13">
-        <f>IF(ISBLANK(B13),"", (G13*H13*(1 - E13 - F13) * J13*L13)+(G13*H13*I13*J13*N13))</f>
+        <f t="shared" si="5"/>
         <v>65.799359999999979</v>
       </c>
       <c r="P13">
-        <f>IF(ISBLANK(A13), "", IF(A13="yes", 1, 0))</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Q13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>0.24</v>
       </c>
       <c r="R13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>15.791846399999994</v>
       </c>
       <c r="S13">
-        <f>IF(ISBLANK(B13),"",$W$8)</f>
+        <f t="shared" si="7"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="T13">
-        <f>IF(ISBLANK(B13), "", R13*S13*$W$10/1000)</f>
-        <v>2.7297334491428559E-4</v>
+        <f t="shared" si="8"/>
+        <v>2.7272518732799988E-4</v>
       </c>
       <c r="V13" t="s">
         <v>4</v>
@@ -3230,7 +3247,7 @@
       <c r="C14" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="13" t="s">
         <v>61</v>
       </c>
       <c r="E14">
@@ -3244,55 +3261,55 @@
         <v>19000</v>
       </c>
       <c r="H14" s="12">
-        <f>IF(ISBLANK($B14), "", VLOOKUP($C14, $V$22:$AD$39, 2, FALSE))</f>
+        <f t="shared" si="0"/>
         <v>1.37</v>
       </c>
       <c r="I14" s="12">
-        <f>IF(ISBLANK($B14), "", VLOOKUP($C14, $V$22:$AD$39, 3, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>0.51</v>
       </c>
       <c r="J14" s="12">
-        <f>IF(ISBLANK($B14), "", VLOOKUP($C14, $V$22:$AD$39, 4, FALSE))</f>
+        <f t="shared" si="2"/>
         <v>0.87</v>
       </c>
       <c r="K14" s="12">
-        <f>IF(ISBLANK($B14), "", VLOOKUP($C14, $V$22:$AD$39, 6, FALSE))</f>
+        <f t="shared" si="3"/>
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="L14" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="M14" s="12">
-        <f>IF(ISBLANK($B14), "", VLOOKUP($C14, $V$22:$AD$39, 7, FALSE))</f>
+        <f t="shared" si="4"/>
         <v>0.01</v>
       </c>
       <c r="N14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>0.01</v>
       </c>
       <c r="O14">
-        <f>IF(ISBLANK(B14),"", (G14*H14*(1 - E14 - F14) * J14*L14)+(G14*H14*I14*J14*N14))</f>
+        <f t="shared" si="5"/>
         <v>243.89849700000002</v>
       </c>
       <c r="P14">
-        <f>IF(ISBLANK(A14), "", IF(A14="yes", 1, 0))</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>0.24</v>
       </c>
       <c r="R14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S14">
-        <f>IF(ISBLANK(B14),"",$W$8)</f>
+        <f t="shared" si="7"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="T14">
-        <f>IF(ISBLANK(B14), "", R14*S14*$W$10/1000)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V14" s="2" t="s">
@@ -3308,7 +3325,7 @@
     <row r="15" spans="1:24">
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
-      <c r="D15" s="14"/>
+      <c r="D15" s="13"/>
       <c r="H15" s="12"/>
       <c r="I15" s="12"/>
       <c r="J15" s="12"/>
@@ -3328,7 +3345,7 @@
     <row r="16" spans="1:24">
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
-      <c r="D16" s="14"/>
+      <c r="D16" s="13"/>
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
       <c r="J16" s="12"/>
@@ -3342,7 +3359,7 @@
     <row r="17" spans="2:30">
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
-      <c r="D17" s="14"/>
+      <c r="D17" s="13"/>
       <c r="H17" s="12"/>
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
@@ -3353,7 +3370,7 @@
     <row r="18" spans="2:30">
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
-      <c r="D18" s="14"/>
+      <c r="D18" s="13"/>
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
@@ -3366,7 +3383,7 @@
     <row r="19" spans="2:30">
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
-      <c r="D19" s="14"/>
+      <c r="D19" s="13"/>
       <c r="H19" s="12"/>
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
@@ -3379,7 +3396,7 @@
     <row r="20" spans="2:30">
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
-      <c r="D20" s="14"/>
+      <c r="D20" s="13"/>
       <c r="H20" s="12"/>
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>

--- a/packages/calculators/src/modules/test/6.3-leaching-runoff.xlsx
+++ b/packages/calculators/src/modules/test/6.3-leaching-runoff.xlsx
@@ -2577,7 +2577,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="O5">
-        <f t="shared" ref="O5:O14" si="5">IF(ISBLANK(B5),"", (G5*H5*(1 - E5 - F5) * J5*L5)+(G5*H5*I5*J5*N5))</f>
+        <f t="shared" ref="O5:O14" si="5">IF(ISBLANK(B5),"", (G5*H5*(1 - IF(ISNUMBER(VLOOKUP($C5, $V$22:$AD$39, 8, FALSE)), E5, 0) - F5) * J5*L5)+(G5*H5*I5*J5*N5))</f>
         <v>3.5750000000000002</v>
       </c>
       <c r="P5">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="O9">
         <f t="shared" si="5"/>
-        <v>0.35700000000000109</v>
+        <v>5.117</v>
       </c>
       <c r="P9">
         <f t="shared" si="6"/>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="R9">
         <f t="shared" si="12"/>
-        <v>8.5680000000000256E-2</v>
+        <v>1.22808</v>
       </c>
       <c r="S9">
         <f t="shared" si="7"/>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="T9">
         <f t="shared" si="8"/>
-        <v>1.4796936000000045E-6</v>
+        <v>2.1208941599999998e-05</v>
       </c>
       <c r="V9" s="2" t="s">
         <v>38</v>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="O10">
         <f t="shared" si="5"/>
-        <v>-2.1675000000000013</v>
+        <v>5.4825</v>
       </c>
       <c r="P10">
         <f t="shared" si="6"/>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="R10">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="S10">
         <f t="shared" si="7"/>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="T10">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="V10" t="s">
         <v>2</v>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="O11">
         <f t="shared" si="5"/>
-        <v>273.60000000000002</v>
+        <v>355.68</v>
       </c>
       <c r="P11">
         <f t="shared" si="6"/>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="R11">
         <f t="shared" si="12"/>
-        <v>65.664000000000001</v>
+        <v>85.36319999999999</v>
       </c>
       <c r="S11">
         <f t="shared" si="7"/>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="T11">
         <f t="shared" si="8"/>
-        <v>1.1340172799999999E-3</v>
+        <v>0.0014742224639999997</v>
       </c>
       <c r="V11" s="2"/>
       <c r="W11" s="2"/>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="O12">
         <f t="shared" si="5"/>
-        <v>94.248000000000005</v>
+        <v>134.64000000000001</v>
       </c>
       <c r="P12">
         <f t="shared" si="6"/>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="R12">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="S12">
         <f t="shared" si="7"/>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="T12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="V12" s="2" t="s">
         <v>3</v>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="O13">
         <f t="shared" si="5"/>
-        <v>65.799359999999979</v>
+        <v>104.00544</v>
       </c>
       <c r="P13">
         <f t="shared" si="6"/>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="R13">
         <f t="shared" si="12"/>
-        <v>15.791846399999994</v>
+        <v>24.961305599999996</v>
       </c>
       <c r="S13">
         <f t="shared" si="7"/>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="T13">
         <f t="shared" si="8"/>
-        <v>2.7272518732799988E-4</v>
+        <v>0.00043108174771199994</v>
       </c>
       <c r="V13" t="s">
         <v>4</v>
